--- a/data/output/authors_orcid_names_elastic.xlsx
+++ b/data/output/authors_orcid_names_elastic.xlsx
@@ -481,40 +481,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-31T07:04:21Z</t>
+          <t>2026-04-11T15:59:40Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['50|dedup_wf_001::5ab4d3eee8a62e678110f1611761bb69']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XR71-ZM27']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['lang', 'hist']</t>
+          <t>['geo', 'socio']</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0000-0002-1588-0683</t>
+          <t>Ana Morales, 0000-0001-6969-2883</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thiago Lima Nicodemo</t>
+          <t>Ana Morales</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>__yGdlcy3e2m0M8R9H4gLU6</t>
+          <t>_ana_morales_3mGc2R6NYalGGGePNQM5k</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0000-0002-1588-0683</t>
+          <t>0000-0001-6969-2883</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -525,7 +525,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>orcid only</t>
+          <t>orcid embedded in name</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -537,40 +537,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-11T15:59:40Z</t>
+          <t>2026-06-14T14:12:14Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XR71-ZM27']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['geo', 'socio']</t>
+          <t>['edu', 'demo']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ana Morales, 0000-0001-6969-2883</t>
+          <t>Anne Lutomia, 0000-0001-6029-8783</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ana Morales</t>
+          <t>Anne Namatsi Lutomia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>_ana_morales_3mGc2R6NYalGGGePNQM5k</t>
+          <t>_anne_lutomia_qPc5d120hLDhlDGt0zvkh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0000-0001-6969-2883</t>
+          <t>0000-0001-6029-8783</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -705,40 +705,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-14T14:12:14Z</t>
+          <t>2025-10-31T07:04:21Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
+          <t>['50|dedup_wf_001::5ab4d3eee8a62e678110f1611761bb69']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['edu', 'demo']</t>
+          <t>['lang', 'hist']</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anne Lutomia, 0000-0001-6029-8783</t>
+          <t>0000-0002-1588-0683</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anne Namatsi Lutomia</t>
+          <t>Thiago Lima Nicodemo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>_anne_lutomia_qPc5d120hLDhlDGt0zvkh</t>
+          <t>__yGdlcy3e2m0M8R9H4gLU6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0000-0001-6029-8783</t>
+          <t>0000-0002-1588-0683</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>orcid embedded in name</t>
+          <t>orcid only</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -873,42 +873,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10T23:52:04Z</t>
+          <t>2025-11-05T10:56:14Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7MK6B49']</t>
+          <t>['ftzenodo:oai:zenodo.org:8081747']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['stat', 'litt']</t>
+          <t>['psy', 'envir']</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Corey S Seliger, 0000-0001-6100-3959</t>
+          <t>by Farzad Saffari 1,2,*ORCID,Sahar Zarei 1,3ORCID,Shobhit Kakaria 4ORCID,Enrique Bigné 4ORCID,Luis E. Bruni</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Corey Seliger</t>
+          <t>By Farzad Saffari 1,2,*,Sahar Zarei 1,3Orcid,Shobhit Kakaria 4Orcid,Enrique Bigné 4Orcid,Luis E. Bruni</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>_corey_s_seliger_Fa5tC9R7eFp_X_pAfxOfG</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0000-0001-6100-3959</t>
-        </is>
-      </c>
+          <t>_by_farzad_saffari__2PWuK4THxcLBD1-x6po7h</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>1</v>
       </c>
@@ -917,56 +913,56 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>orcid embedded in name</t>
+          <t>stray orcid word</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>orcid api</t>
+          <t>cleaned in place</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-12T15:00:34Z</t>
+          <t>2026-08-10T23:52:04Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XYK9-C767', 'ftpurdueunivpurr:https:__doi.org_10.4231_YSQA-C238', 'ftpurdueunivpurr:https:__doi.org_10.4231_39ZC-PV13', 'ftpurdueunivpurr:https:__doi.org_10.4231_5SC3-TF15', 'ftpurdueunivpurr:https:__doi.org_10.4231_DA5R-5M09', 'ftpurdueunivpurr:https:__doi.org_10.4231_Y0PA-B148', 'ftpurdueunivpurr:https:__doi.org_10.4231_SBGE-CG65', 'ftpurdueunivpurr:https:__doi.org_10.4231_26RX-W702', 'ftpurdueunivpurr:https:__doi.org_10.4231_MKD9-AT22', 'ftpurdueunivpurr:https:__doi.org_10.4231_ZY99-QF11', 'ftpurdueunivpurr:https:__doi.org_10.4231_TV7R-AG03', 'ftpurdueunivpurr:https:__doi.org_10.4231_7HAJ-WR33', 'ftpurdueunivpurr:https:__doi.org_10.4231_25NP-AF77', 'ftpurdueunivpurr:https:__doi.org_10.4231_JBFW-7V88', 'ftpurdueunivpurr:https:__doi.org_10.4231_VM0K-6320', 'ftpurdueunivpurr:https:__doi.org_10.4231_WXST-HY10', 'ftpurdueunivpurr:https:__doi.org_10.4231_TAVZ-T804', 'ftpurdueunivpurr:https:__doi.org_10.4231_ER7H-9390']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7MK6B49']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['art', 'hist', 'musiq', 'archeo', 'scipo', 'phil']</t>
+          <t>['stat', 'litt']</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daniel W Smith, 0009-0007-2293-2713</t>
+          <t>Corey S Seliger, 0000-0001-6100-3959</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Daniel Smith</t>
+          <t>Corey Seliger</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>_daniel_w_smith_Au81AGAlrzUpPQVJZSeDl</t>
+          <t>_corey_s_seliger_Fa5tC9R7eFp_X_pAfxOfG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0009-0007-2293-2713</t>
+          <t>0000-0001-6100-3959</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -985,44 +981,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-11T10:33:31Z</t>
+          <t>2026-06-12T15:00:34Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_AAD7-2B97']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XYK9-C767', 'ftpurdueunivpurr:https:__doi.org_10.4231_YSQA-C238', 'ftpurdueunivpurr:https:__doi.org_10.4231_39ZC-PV13', 'ftpurdueunivpurr:https:__doi.org_10.4231_5SC3-TF15', 'ftpurdueunivpurr:https:__doi.org_10.4231_DA5R-5M09', 'ftpurdueunivpurr:https:__doi.org_10.4231_Y0PA-B148', 'ftpurdueunivpurr:https:__doi.org_10.4231_SBGE-CG65', 'ftpurdueunivpurr:https:__doi.org_10.4231_26RX-W702', 'ftpurdueunivpurr:https:__doi.org_10.4231_MKD9-AT22', 'ftpurdueunivpurr:https:__doi.org_10.4231_ZY99-QF11', 'ftpurdueunivpurr:https:__doi.org_10.4231_TV7R-AG03', 'ftpurdueunivpurr:https:__doi.org_10.4231_7HAJ-WR33', 'ftpurdueunivpurr:https:__doi.org_10.4231_25NP-AF77', 'ftpurdueunivpurr:https:__doi.org_10.4231_JBFW-7V88', 'ftpurdueunivpurr:https:__doi.org_10.4231_VM0K-6320', 'ftpurdueunivpurr:https:__doi.org_10.4231_WXST-HY10', 'ftpurdueunivpurr:https:__doi.org_10.4231_TAVZ-T804', 'ftpurdueunivpurr:https:__doi.org_10.4231_ER7H-9390']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['geo', 'art']</t>
+          <t>['art', 'hist', 'musiq', 'archeo', 'scipo', 'phil']</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Danielle Winter Lay, 0000-0002-0225-9628</t>
+          <t>Daniel W Smith, 0009-0007-2293-2713</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Danielle Winter Lay</t>
+          <t>Daniel Smith</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>_danielle_winter_lay_JZDpxEWGib1DNZnKq9rmm</t>
+          <t>_daniel_w_smith_Au81AGAlrzUpPQVJZSeDl</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0000-0002-0225-9628</t>
+          <t>0009-0007-2293-2713</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1041,40 +1037,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-14T23:28:47Z</t>
+          <t>2026-04-11T10:33:31Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7PN93M4']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_AAD7-2B97']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['geo', 'art']</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elena E. Benedicto, 0000-0001-7797-3159</t>
+          <t>Danielle Winter Lay, 0000-0002-0225-9628</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Elena E. Benedicto</t>
+          <t>Danielle Winter Lay</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>_elena_e_benedicto_XwlDJ1v_GZnwW54Bqo5tl</t>
+          <t>_danielle_winter_lay_JZDpxEWGib1DNZnKq9rmm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0000-0001-7797-3159</t>
+          <t>0000-0002-0225-9628</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1097,17 +1093,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-11T05:21:29Z</t>
+          <t>2026-08-14T23:28:47Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_ADDK-QB60']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7PN93M4']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['stat', 'envir']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1115,22 +1111,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elizabeth B Allmon, 0000-0002-8279-4013</t>
+          <t>Elena E. Benedicto, 0000-0001-7797-3159</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Elizabeth Allmon</t>
+          <t>Elena E. Benedicto</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>_elizabeth_b_allmon_BAS8RF9XBoV-oPcgO0swk</t>
+          <t>_elena_e_benedicto_XwlDJ1v_GZnwW54Bqo5tl</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0000-0002-8279-4013</t>
+          <t>0000-0001-7797-3159</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1153,17 +1149,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-11T05:21:42Z</t>
+          <t>2026-04-11T05:21:29Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_3RX2-WR09']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_ADDK-QB60']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['stat', 'demo']</t>
+          <t>['stat', 'envir']</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1181,7 +1177,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>_elizabeth_b_allmon_VKgAV7KclN_r4kPTMN_IZ</t>
+          <t>_elizabeth_b_allmon_BAS8RF9XBoV-oPcgO0swk</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1209,40 +1205,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04T19:12:11Z</t>
+          <t>2026-04-11T05:21:42Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_06VT-DH11']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_3RX2-WR09']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['class', 'lang']</t>
+          <t>['stat', 'demo']</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erin K Moodie, 0009-0005-4338-5355</t>
+          <t>Elizabeth B Allmon, 0000-0002-8279-4013</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erin K. Moodie</t>
+          <t>Elizabeth Allmon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>_erin_k_moodie_TmtEmM-XVGUlKJsvm8xPS</t>
+          <t>_elizabeth_b_allmon_VKgAV7KclN_r4kPTMN_IZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0009-0005-4338-5355</t>
+          <t>0000-0002-8279-4013</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1265,40 +1261,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-07T18:46:03Z</t>
+          <t>2026-08-04T19:12:11Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['ftunivmonsojs:oai:orbi.umons.ac.be:20.500.12907_44171']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_06VT-DH11']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['geo', 'envir']</t>
+          <t>['class', 'lang']</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{lastName:Kilani, firstNames:Moez,affiliations: Lille Economie et Management, UMR 9221, Département Economie Gestion, Université du Littoral Côte d’Opale, Dunkerque, France ,ids: SC:23090588900OR:0000-0002-0049-8027</t>
+          <t>Erin K Moodie, 0009-0005-4338-5355</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kilani Moez</t>
+          <t>Erin K. Moodie</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>_firstnames_moez_lastname_kilani__Vs0KfNp56IwExDs6b6Son</t>
+          <t>_erin_k_moodie_TmtEmM-XVGUlKJsvm8xPS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0000-0002-0049-8027</t>
+          <t>0009-0005-4338-5355</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1321,40 +1317,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-14T12:04:23Z</t>
+          <t>2026-06-07T18:46:03Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_SWE2-FX07']</t>
+          <t>['ftunivmonsojs:oai:orbi.umons.ac.be:20.500.12907_44171']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['archeo', 'class']</t>
+          <t>['geo', 'envir']</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Günder Varinlioglu, 0000-0001-9435-9791</t>
+          <t>{lastName:Kilani, firstNames:Moez,affiliations: Lille Economie et Management, UMR 9221, Département Economie Gestion, Université du Littoral Côte d’Opale, Dunkerque, France ,ids: SC:23090588900OR:0000-0002-0049-8027</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Günder Varinlioğlu</t>
+          <t>Kilani Moez</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>_gunder_varinlioglu_1bj7nZD4v7mqNVrMh6ei8</t>
+          <t>_firstnames_moez_lastname_kilani__Vs0KfNp56IwExDs6b6Son</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0000-0001-9435-9791</t>
+          <t>0000-0002-0049-8027</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1377,44 +1373,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20T00:46:46Z</t>
+          <t>2026-06-14T12:04:23Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['ftangliruskinfig:oai:figshare.com:article_29994145', 'ftbritmuseumfig:oai:figshare.com:article_29618312', 'ftbritmuseumfig:oai:figshare.com:article_29994145', 'ftcardiffmetufig:oai:figshare.com:article_29994145']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_SWE2-FX07']</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['eco', 'manag']</t>
+          <t>['archeo', 'class']</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0009-0001-3381-5957 Hogberg</t>
+          <t>Günder Varinlioglu, 0000-0001-9435-9791</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Denis P.</t>
+          <t>Günder Varinlioğlu</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>_hogberg_Uk7EVCRZeJq5JCLFlXSK9</t>
+          <t>_gunder_varinlioglu_1bj7nZD4v7mqNVrMh6ei8</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0009-0001-3381-5957</t>
+          <t>0000-0001-9435-9791</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -1433,44 +1429,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01T18:16:22Z</t>
+          <t>2026-08-20T00:46:46Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_CNW9-GS78']</t>
+          <t>['ftangliruskinfig:oai:figshare.com:article_29994145', 'ftbritmuseumfig:oai:figshare.com:article_29618312', 'ftbritmuseumfig:oai:figshare.com:article_29994145', 'ftcardiffmetufig:oai:figshare.com:article_29994145']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['geo', 'info']</t>
+          <t>['eco', 'manag']</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hwanseok Song, 0000-0003-0995-0291</t>
+          <t>0009-0001-3381-5957 Hogberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwanseok Song</t>
+          <t>Denis P.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>_hwanseok_song_7TOKZgal5kRab8-DA7JSh</t>
+          <t>_hogberg_Uk7EVCRZeJq5JCLFlXSK9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0000-0003-0995-0291</t>
+          <t>0009-0001-3381-5957</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -1489,40 +1485,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-11T10:33:30Z</t>
+          <t>2026-08-01T18:16:22Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_AAD7-2B97']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_CNW9-GS78']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['geo', 'art']</t>
+          <t>['geo', 'info']</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jacob Daniel Hosen, 0000-0003-2559-0687</t>
+          <t>Hwanseok Song, 0000-0003-0995-0291</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jacob Hosen</t>
+          <t>Hwanseok Song</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>_jacob_daniel_hosen_AawL63_ky2GEHMy1dSi8_</t>
+          <t>_hwanseok_song_7TOKZgal5kRab8-DA7JSh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0000-0003-2559-0687</t>
+          <t>0000-0003-0995-0291</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1545,40 +1541,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-14T14:12:13Z</t>
+          <t>2026-04-11T10:33:30Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_AAD7-2B97']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['edu', 'demo']</t>
+          <t>['geo', 'art']</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>John William Medendorp, 0000-0003-2527-7324</t>
+          <t>Jacob Daniel Hosen, 0000-0003-2559-0687</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>John William Medendorp</t>
+          <t>Jacob Hosen</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>_john_william_medendorp_m5WZV3O2iW1ZfsAZ1eVnn</t>
+          <t>_jacob_daniel_hosen_AawL63_ky2GEHMy1dSi8_</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0000-0003-2527-7324</t>
+          <t>0000-0003-2559-0687</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1601,40 +1597,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-10T23:52:04Z</t>
+          <t>2026-06-14T14:12:13Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7J38QSP']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['anthro-se']</t>
+          <t>['edu', 'demo']</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jonathan Bauchet, 0000-0002-0583-5678</t>
+          <t>John William Medendorp, 0000-0003-2527-7324</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jonathan Bauchet</t>
+          <t>John William Medendorp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>_jonathan_bauchet_L3JTtCpMO2_4poLkKRzgC</t>
+          <t>_john_william_medendorp_m5WZV3O2iW1ZfsAZ1eVnn</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0000-0002-0583-5678</t>
+          <t>0000-0003-2527-7324</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1657,40 +1653,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-29T04:28:43Z</t>
+          <t>2026-08-10T23:52:04Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_AG8V-DM52']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7J38QSP']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['lang', 'psy']</t>
+          <t>['anthro-se']</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Joshua M Alexander, 0000-0002-4292-7109</t>
+          <t>Jonathan Bauchet, 0000-0002-0583-5678</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Joshua Alexander</t>
+          <t>Jonathan Bauchet</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>_joshua_m_alexander_qTaRlH0efpnHcx8vgbiGo</t>
+          <t>_jonathan_bauchet_L3JTtCpMO2_4poLkKRzgC</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0000-0002-4292-7109</t>
+          <t>0000-0002-0583-5678</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1713,40 +1709,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-14T14:12:13Z</t>
+          <t>2026-05-29T04:28:43Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_AG8V-DM52']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['edu', 'demo']</t>
+          <t>['lang', 'psy']</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Julia Bello-Bravo, 0000-0002-1710-4725</t>
+          <t>Joshua M Alexander, 0000-0002-4292-7109</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Julia Bello-Bravo</t>
+          <t>Joshua Alexander</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>_julia_bello_bravo_0j6cngtQnohzGm6D2ZMnH</t>
+          <t>_joshua_m_alexander_qTaRlH0efpnHcx8vgbiGo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0000-0002-1710-4725</t>
+          <t>0000-0002-4292-7109</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1769,40 +1765,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-15T11:23:42Z</t>
+          <t>2026-06-14T14:12:13Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7BR8Q59']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['lang', 'phil']</t>
+          <t>['edu', 'demo']</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Linda S. Prokopy, 0000-0001-7076-0046</t>
+          <t>Julia Bello-Bravo, 0000-0002-1710-4725</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linda Prokopy</t>
+          <t>Julia Bello-Bravo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>_linda_s_prokopy_y82nkjDg5W_J9cr2zQs4l</t>
+          <t>_julia_bello_bravo_0j6cngtQnohzGm6D2ZMnH</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0000-0001-7076-0046</t>
+          <t>0000-0002-1710-4725</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1825,40 +1821,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-13T10:31:23Z</t>
+          <t>2026-06-15T11:23:42Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['ftangliruskinfig:oai:figshare.com:article_29973217']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7BR8Q59']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['edu', 'phil']</t>
+          <t>['lang', 'phil']</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0000-0002-9888-6457 Maniraho</t>
+          <t>Linda S. Prokopy, 0000-0001-7076-0046</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jean Francois Maniraho</t>
+          <t>Linda Prokopy</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>_maniraho_5VQiTIazfFQogqkvxzrjG</t>
+          <t>_linda_s_prokopy_y82nkjDg5W_J9cr2zQs4l</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0000-0002-9888-6457</t>
+          <t>0000-0001-7076-0046</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1881,40 +1877,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-11T13:43:30Z</t>
+          <t>2026-06-13T10:31:23Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_0JKD-A159']</t>
+          <t>['ftangliruskinfig:oai:figshare.com:article_29973217']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['envir', 'geo']</t>
+          <t>['edu', 'phil']</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Margaret W Gitau, 0000-0002-4931-7047</t>
+          <t>0000-0002-9888-6457 Maniraho</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Margaret Gitau</t>
+          <t>Jean Francois Maniraho</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>_margaret_w_gitau_dZNCtb8VK-S3uiBkCI5yI</t>
+          <t>_maniraho_5VQiTIazfFQogqkvxzrjG</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0000-0002-4931-7047</t>
+          <t>0000-0002-9888-6457</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1937,40 +1933,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-29T04:28:05Z</t>
+          <t>2026-04-11T13:43:30Z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_C6E8-JM62']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_0JKD-A159']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['info', 'art']</t>
+          <t>['envir', 'geo']</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Matthew N. Hannah, 0000-0002-9060-4427</t>
+          <t>Margaret W Gitau, 0000-0002-4931-7047</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Matthew Hannah</t>
+          <t>Margaret Gitau</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>_matthew_n_hannah_QaMsOb8w_aAQkQ_SEACkn</t>
+          <t>_margaret_w_gitau_dZNCtb8VK-S3uiBkCI5yI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0000-0002-9060-4427</t>
+          <t>0000-0002-4931-7047</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1993,40 +1989,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-11T06:39:26Z</t>
+          <t>2026-05-29T04:28:05Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_VZDF-VX48']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_C6E8-JM62']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['geo', 'envir']</t>
+          <t>['info', 'art']</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Md. Samiul Basir, 0000-0003-1753-7464</t>
+          <t>Matthew N. Hannah, 0000-0002-9060-4427</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Md. Samiul Basir</t>
+          <t>Matthew Hannah</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>_md_samiul_basir_-BmgMETqIyrO-Fvt50Dx4</t>
+          <t>_matthew_n_hannah_QaMsOb8w_aAQkQ_SEACkn</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0000-0003-1753-7464</t>
+          <t>0000-0002-9060-4427</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2049,40 +2045,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-15T11:23:42Z</t>
+          <t>2026-04-11T06:39:26Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7BR8Q59']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_VZDF-VX48']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['lang', 'phil']</t>
+          <t>['geo', 'envir']</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Melissa J. Widhalm, 0000-0002-6099-4006</t>
+          <t>Md. Samiul Basir, 0000-0003-1753-7464</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Melissa Widhalm</t>
+          <t>Md. Samiul Basir</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>_melissa_j_widhalm_5lCASTY2npdUyzwhMffA6</t>
+          <t>_md_samiul_basir_-BmgMETqIyrO-Fvt50Dx4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0000-0002-6099-4006</t>
+          <t>0000-0003-1753-7464</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2105,40 +2101,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-11T13:43:31Z</t>
+          <t>2026-06-15T11:23:42Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_0JKD-A159']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7BR8Q59']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['envir', 'geo']</t>
+          <t>['lang', 'phil']</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mitchell R Tuinstra, 0000-0002-5322-6519</t>
+          <t>Melissa J. Widhalm, 0000-0002-6099-4006</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mitchell Tuinstra</t>
+          <t>Melissa Widhalm</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>_mitchell_r_tuinstra_-rlG070yHkD_r3KpE_FJE</t>
+          <t>_melissa_j_widhalm_5lCASTY2npdUyzwhMffA6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0000-0002-5322-6519</t>
+          <t>0000-0002-6099-4006</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2161,44 +2157,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07T23:33:43Z</t>
+          <t>2026-04-11T13:43:31Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_SWE2-FX07', 'ftpurdueunivpurr:https:__doi.org_10.4231_25Y6-BY07', 'ftpurdueunivpurr:https:__doi.org_10.4231_08XY-XJ30', 'ftpurdueunivpurr:https:__doi.org_10.4231_B6F2-9K09', 'ftpurdueunivpurr:https:__doi.org_10.4231_WF3E-2W39', 'ftpurdueunivpurr:https:__doi.org_10.4231_MEPT-Q457', 'ftpurdueunivpurr:https:__doi.org_10.4231_K2MY-AV11', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7H993DF', 'ftpurdueunivpurr:https:__doi.org_10.4231_0PX3-T517', 'ftpurdueunivpurr:https:__doi.org_10.4231_WGXJ-TE67', 'ftpurdueunivpurr:https:__doi.org_10.4231_Z4YN-F967', 'ftpurdueunivpurr:https:__doi.org_10.4231_0EAN-DE59', 'ftpurdueunivpurr:https:__doi.org_10.4231_GMRG-8K41', 'ftpurdueunivpurr:https:__doi.org_10.4231_9SKX-FD80', 'ftpurdueunivpurr:https:__doi.org_10.4231_3P20-MG91', 'ftpurdueunivpurr:https:__doi.org_10.4231_1RAM-JR22', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7513WDT', 'ftpurdueunivpurr:https:__doi.org_10.4231_R78S4N47', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7J964MQ', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7WM1BMH', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7RV0KX7', 'ftpurdueunivpurr:https:__doi.org_10.4231_R71834QX', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7DJ5CVJ', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7P26WB2']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_0JKD-A159']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['archeo', 'class']</t>
+          <t>['envir', 'geo']</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nicholas Kregotis Rauh, 0000-0001-6924-1804</t>
+          <t>Mitchell R Tuinstra, 0000-0002-5322-6519</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nicholas Rauh</t>
+          <t>Mitchell Tuinstra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>_nicholas_kregotis_rauh_5i2sn69u7SiaAza9mpSG2</t>
+          <t>_mitchell_r_tuinstra_-rlG070yHkD_r3KpE_FJE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0000-0001-6924-1804</t>
+          <t>0000-0002-5322-6519</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -2217,12 +2213,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-14T12:04:23Z</t>
+          <t>2026-08-07T23:33:43Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_SWE2-FX07']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_SWE2-FX07', 'ftpurdueunivpurr:https:__doi.org_10.4231_25Y6-BY07', 'ftpurdueunivpurr:https:__doi.org_10.4231_08XY-XJ30', 'ftpurdueunivpurr:https:__doi.org_10.4231_B6F2-9K09', 'ftpurdueunivpurr:https:__doi.org_10.4231_WF3E-2W39', 'ftpurdueunivpurr:https:__doi.org_10.4231_MEPT-Q457', 'ftpurdueunivpurr:https:__doi.org_10.4231_K2MY-AV11', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7H993DF', 'ftpurdueunivpurr:https:__doi.org_10.4231_0PX3-T517', 'ftpurdueunivpurr:https:__doi.org_10.4231_WGXJ-TE67', 'ftpurdueunivpurr:https:__doi.org_10.4231_Z4YN-F967', 'ftpurdueunivpurr:https:__doi.org_10.4231_0EAN-DE59', 'ftpurdueunivpurr:https:__doi.org_10.4231_GMRG-8K41', 'ftpurdueunivpurr:https:__doi.org_10.4231_9SKX-FD80', 'ftpurdueunivpurr:https:__doi.org_10.4231_3P20-MG91', 'ftpurdueunivpurr:https:__doi.org_10.4231_1RAM-JR22', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7513WDT', 'ftpurdueunivpurr:https:__doi.org_10.4231_R78S4N47', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7J964MQ', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7WM1BMH', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7RV0KX7', 'ftpurdueunivpurr:https:__doi.org_10.4231_R71834QX', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7DJ5CVJ', 'ftpurdueunivpurr:https:__doi.org_10.4231_R7P26WB2']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2231,30 +2227,30 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Noah Kaye, 0000-0001-8975-2871</t>
+          <t>Nicholas Kregotis Rauh, 0000-0001-6924-1804</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Noah Kaye</t>
+          <t>Nicholas Rauh</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>_noah_kaye_UzbjQgGJaricx-fqA-m9a</t>
+          <t>_nicholas_kregotis_rauh_5i2sn69u7SiaAza9mpSG2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0000-0001-8975-2871</t>
+          <t>0000-0001-6924-1804</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -2273,40 +2269,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-14T14:12:13Z</t>
+          <t>2026-06-14T12:04:23Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_SWE2-FX07']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['edu', 'demo']</t>
+          <t>['archeo', 'class']</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norman Peter Reeves, 0000-0001-5021-7839</t>
+          <t>Noah Kaye, 0000-0001-8975-2871</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>N. Peter Reeves</t>
+          <t>Noah Kaye</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>_norman_peter_reeves_mN2iC-gCmnXCNFbGsa0XI</t>
+          <t>_noah_kaye_UzbjQgGJaricx-fqA-m9a</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0000-0001-5021-7839</t>
+          <t>0000-0001-8975-2871</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2329,40 +2325,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-11-06T01:46:28Z</t>
+          <t>2026-06-14T14:12:13Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll5_3029']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['manag', 'eco']</t>
+          <t>['edu', 'demo']</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>| orcid:0000-0002-8706-2516</t>
+          <t>Norman Peter Reeves, 0000-0001-5021-7839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Suresh Chandra Babu</t>
+          <t>N. Peter Reeves</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>_orcid__2hMimQKEiEeTzgH3Yw3Rh</t>
+          <t>_norman_peter_reeves_mN2iC-gCmnXCNFbGsa0XI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0000-0002-8706-2516</t>
+          <t>0000-0001-5021-7839</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2373,7 +2369,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>orcid only</t>
+          <t>orcid embedded in name</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2385,12 +2381,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-11-06T05:46:24Z</t>
+          <t>2025-11-06T01:46:28Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_124978']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll5_3029']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2403,22 +2399,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>| orcid:0000-0003-2404-7826</t>
+          <t>| orcid:0000-0002-8706-2516</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bjorn Van Campenhout</t>
+          <t>Suresh Chandra Babu</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>_orcid__3LcYJWuKZgOWsVfEIla-6</t>
+          <t>_orcid__2hMimQKEiEeTzgH3Yw3Rh</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0000-0003-2404-7826</t>
+          <t>0000-0002-8706-2516</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2441,17 +2437,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-11-06T01:43:12Z</t>
+          <t>2025-11-06T05:46:24Z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_126265', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1926']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_124978']</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['droit', 'hist']</t>
+          <t>['manag', 'eco']</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2459,26 +2455,26 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>| orcid:0000-0002-3324-1324</t>
+          <t>| orcid:0000-0003-2404-7826</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Patricia Zambrano</t>
+          <t>Bjorn Van Campenhout</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>_orcid__4txzOUqEmHR61Hw39r7En</t>
+          <t>_orcid__3LcYJWuKZgOWsVfEIla-6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0000-0002-3324-1324</t>
+          <t>0000-0003-2404-7826</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -2497,44 +2493,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-06T09:02:13Z</t>
+          <t>2025-11-06T01:43:12Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_128016']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_126265', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1926']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['manag', 'eco']</t>
+          <t>['droit', 'hist']</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>| :0000-0001-8793-1200</t>
+          <t>| orcid:0000-0002-3324-1324</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Patrick S Ward</t>
+          <t>Patricia Zambrano</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>_orcid__542hraj6pcdbIB_4_h9ws</t>
+          <t>_orcid__4txzOUqEmHR61Hw39r7En</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0000-0001-8793-1200</t>
+          <t>0000-0002-3324-1324</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -2553,17 +2549,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-10T13:49:10Z</t>
+          <t>2026-02-06T09:02:13Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1894']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_128016']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['envir', 'geo']</t>
+          <t>['manag', 'eco']</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2571,22 +2567,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>| :0000-0001-7553-2464</t>
+          <t>| :0000-0001-8793-1200</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yanyan Liu</t>
+          <t>Patrick S Ward</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>_orcid__6bWuO3fN9Ccff4ejYT1YG</t>
+          <t>_orcid__542hraj6pcdbIB_4_h9ws</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0000-0001-7553-2464</t>
+          <t>0000-0001-8793-1200</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2609,17 +2605,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-09T17:54:37Z</t>
+          <t>2026-03-10T13:49:10Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_761', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_23338', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_130648', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1345', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_2417', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_18394', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_29949', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1642', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_3453']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1894']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['geo', 'envir', 'demo', 'scipo', 'eco', 'manag']</t>
+          <t>['envir', 'geo']</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2627,26 +2623,26 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>| :0000-0002-6882-3551</t>
+          <t>| :0000-0001-7553-2464</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tingju Zhu</t>
+          <t>Yanyan Liu</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>_orcid__6nase8ONHT-8tU-yS22h3</t>
+          <t>_orcid__6bWuO3fN9Ccff4ejYT1YG</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0000-0002-6882-3551</t>
+          <t>0000-0001-7553-2464</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -2665,52 +2661,56 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-11-05T10:56:14Z</t>
+          <t>2026-03-09T17:54:37Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['ftzenodo:oai:zenodo.org:8081747']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_761', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_23338', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_130648', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1345', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_2417', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_18394', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_29949', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1642', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll2_3453']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['psy', 'envir']</t>
+          <t>['geo', 'envir', 'demo', 'scipo', 'eco', 'manag']</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>by Farzad Saffari 1,2,*ORCID,Sahar Zarei 1,3ORCID,Shobhit Kakaria 4ORCID,Enrique Bigné 4ORCID,Luis E. Bruni</t>
+          <t>| :0000-0002-6882-3551</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>By Farzad Saffari 1,2,*,Sahar Zarei 1,3Orcid,Shobhit Kakaria 4Orcid,Enrique Bigné 4Orcid,Luis E. Bruni</t>
+          <t>Tingju Zhu</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>_by_farzad_saffari__2PWuK4THxcLBD1-x6po7h</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>_orcid__6nase8ONHT-8tU-yS22h3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0000-0002-6882-3551</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>stray orcid word</t>
+          <t>orcid only</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>cleaned in place</t>
+          <t>orcid api</t>
         </is>
       </c>
     </row>

--- a/data/output/authors_orcid_names_elastic.xlsx
+++ b/data/output/authors_orcid_names_elastic.xlsx
@@ -481,40 +481,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-11T15:59:40Z</t>
+          <t>2026-08-10T23:52:04Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XR71-ZM27']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_01D8-V289']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['geo', 'socio']</t>
+          <t>['demo', 'socio']</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ana Morales, 0000-0001-6969-2883</t>
+          <t>Andrea Demaria, 0000-0002-5450-0444</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ana Morales</t>
+          <t>Andrea L. Demaria</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>_ana_morales_3mGc2R6NYalGGGePNQM5k</t>
+          <t>_andrea_demaria_BeJ9VyDol6i1hMQ5Ck9sm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0000-0001-6969-2883</t>
+          <t>0000-0002-5450-0444</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-14T14:12:14Z</t>
+          <t>2026-06-12T13:30:30Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
+          <t>['ftangliruskinfig:oai:figshare.com:article_29625350']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -551,26 +551,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anne Lutomia, 0000-0001-6029-8783</t>
+          <t>0000-0002-5658-6085 Al Saffar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anne Namatsi Lutomia</t>
+          <t>May Ali Alsaffar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>_anne_lutomia_qPc5d120hLDhlDGt0zvkh</t>
+          <t>_al_saffar_91YLQAAzbumMeER42sOag</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0000-0001-6029-8783</t>
+          <t>0000-0002-5658-6085</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -593,40 +593,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10T23:52:04Z</t>
+          <t>2026-04-11T15:59:40Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_01D8-V289']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XR71-ZM27']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['demo', 'socio']</t>
+          <t>['geo', 'socio']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Andrea Demaria, 0000-0002-5450-0444</t>
+          <t>Ana Morales, 0000-0001-6969-2883</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Andrea L. Demaria</t>
+          <t>Ana Morales</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>_andrea_demaria_BeJ9VyDol6i1hMQ5Ck9sm</t>
+          <t>_ana_morales_3mGc2R6NYalGGGePNQM5k</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0000-0002-5450-0444</t>
+          <t>0000-0001-6969-2883</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -649,12 +649,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-12T13:30:30Z</t>
+          <t>2026-06-14T14:12:14Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['ftangliruskinfig:oai:figshare.com:article_29625350']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -663,26 +663,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0000-0002-5658-6085 Al Saffar</t>
+          <t>Anne Lutomia, 0000-0001-6029-8783</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>May Ali Alsaffar</t>
+          <t>Anne Namatsi Lutomia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>_al_saffar_91YLQAAzbumMeER42sOag</t>
+          <t>_anne_lutomia_qPc5d120hLDhlDGt0zvkh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0000-0002-5658-6085</t>
+          <t>0000-0001-6029-8783</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -705,42 +705,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-31T07:04:21Z</t>
+          <t>2025-11-05T10:56:14Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['50|dedup_wf_001::5ab4d3eee8a62e678110f1611761bb69']</t>
+          <t>['ftzenodo:oai:zenodo.org:8081747']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['lang', 'hist']</t>
+          <t>['psy', 'envir']</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0000-0002-1588-0683</t>
+          <t>by Farzad Saffari 1,2,*ORCID,Sahar Zarei 1,3ORCID,Shobhit Kakaria 4ORCID,Enrique Bigné 4ORCID,Luis E. Bruni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thiago Lima Nicodemo</t>
+          <t>By Farzad Saffari 1,2,*,Sahar Zarei 1,3Orcid,Shobhit Kakaria 4Orcid,Enrique Bigné 4Orcid,Luis E. Bruni</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>__yGdlcy3e2m0M8R9H4gLU6</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0000-0002-1588-0683</t>
-        </is>
-      </c>
+          <t>_by_farzad_saffari__2PWuK4THxcLBD1-x6po7h</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>1</v>
       </c>
@@ -749,52 +745,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>orcid only</t>
+          <t>stray orcid word</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>orcid api</t>
+          <t>cleaned in place</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10T23:52:04Z</t>
+          <t>2025-10-31T07:04:21Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R76Q1V5Q']</t>
+          <t>['50|dedup_wf_001::5ab4d3eee8a62e678110f1611761bb69']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['edu', 'socio']</t>
+          <t>['lang', 'hist']</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chad Laux, 0000-0001-7445-2446</t>
+          <t>0000-0002-1588-0683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chad Laux</t>
+          <t>Thiago Lima Nicodemo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>_chad_laux_P8HwWOySU2u_ccVtBC_FL</t>
+          <t>__yGdlcy3e2m0M8R9H4gLU6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0000-0001-7445-2446</t>
+          <t>0000-0002-1588-0683</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -805,7 +801,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>orcid embedded in name</t>
+          <t>orcid only</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -817,44 +813,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12T15:00:34Z</t>
+          <t>2026-08-10T23:52:04Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XYK9-C767', 'ftpurdueunivpurr:https:__doi.org_10.4231_YSQA-C238', 'ftpurdueunivpurr:https:__doi.org_10.4231_39ZC-PV13', 'ftpurdueunivpurr:https:__doi.org_10.4231_5SC3-TF15', 'ftpurdueunivpurr:https:__doi.org_10.4231_DA5R-5M09', 'ftpurdueunivpurr:https:__doi.org_10.4231_Y0PA-B148', 'ftpurdueunivpurr:https:__doi.org_10.4231_SBGE-CG65', 'ftpurdueunivpurr:https:__doi.org_10.4231_26RX-W702', 'ftpurdueunivpurr:https:__doi.org_10.4231_MKD9-AT22', 'ftpurdueunivpurr:https:__doi.org_10.4231_ZY99-QF11', 'ftpurdueunivpurr:https:__doi.org_10.4231_TV7R-AG03', 'ftpurdueunivpurr:https:__doi.org_10.4231_7HAJ-WR33', 'ftpurdueunivpurr:https:__doi.org_10.4231_25NP-AF77', 'ftpurdueunivpurr:https:__doi.org_10.4231_JBFW-7V88', 'ftpurdueunivpurr:https:__doi.org_10.4231_VM0K-6320', 'ftpurdueunivpurr:https:__doi.org_10.4231_WXST-HY10', 'ftpurdueunivpurr:https:__doi.org_10.4231_TAVZ-T804', 'ftpurdueunivpurr:https:__doi.org_10.4231_ER7H-9390']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R76Q1V5Q']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['art', 'hist', 'musiq', 'archeo', 'scipo', 'phil']</t>
+          <t>['edu', 'socio']</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charles Joseph Stivale, 0000-0001-9893-6197</t>
+          <t>Chad Laux, 0000-0001-7445-2446</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charles Stivale</t>
+          <t>Chad Laux</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>_charles_joseph_stivale_hIFjr8D0GQKZQAvOW-Mep</t>
+          <t>_chad_laux_P8HwWOySU2u_ccVtBC_FL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0000-0001-9893-6197</t>
+          <t>0000-0001-7445-2446</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -873,52 +869,56 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-05T10:56:14Z</t>
+          <t>2026-06-12T15:00:34Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['ftzenodo:oai:zenodo.org:8081747']</t>
+          <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XYK9-C767', 'ftpurdueunivpurr:https:__doi.org_10.4231_YSQA-C238', 'ftpurdueunivpurr:https:__doi.org_10.4231_39ZC-PV13', 'ftpurdueunivpurr:https:__doi.org_10.4231_5SC3-TF15', 'ftpurdueunivpurr:https:__doi.org_10.4231_DA5R-5M09', 'ftpurdueunivpurr:https:__doi.org_10.4231_Y0PA-B148', 'ftpurdueunivpurr:https:__doi.org_10.4231_SBGE-CG65', 'ftpurdueunivpurr:https:__doi.org_10.4231_26RX-W702', 'ftpurdueunivpurr:https:__doi.org_10.4231_MKD9-AT22', 'ftpurdueunivpurr:https:__doi.org_10.4231_ZY99-QF11', 'ftpurdueunivpurr:https:__doi.org_10.4231_TV7R-AG03', 'ftpurdueunivpurr:https:__doi.org_10.4231_7HAJ-WR33', 'ftpurdueunivpurr:https:__doi.org_10.4231_25NP-AF77', 'ftpurdueunivpurr:https:__doi.org_10.4231_JBFW-7V88', 'ftpurdueunivpurr:https:__doi.org_10.4231_VM0K-6320', 'ftpurdueunivpurr:https:__doi.org_10.4231_WXST-HY10', 'ftpurdueunivpurr:https:__doi.org_10.4231_TAVZ-T804', 'ftpurdueunivpurr:https:__doi.org_10.4231_ER7H-9390']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['psy', 'envir']</t>
+          <t>['art', 'hist', 'musiq', 'archeo', 'scipo', 'phil']</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>by Farzad Saffari 1,2,*ORCID,Sahar Zarei 1,3ORCID,Shobhit Kakaria 4ORCID,Enrique Bigné 4ORCID,Luis E. Bruni</t>
+          <t>Charles Joseph Stivale, 0000-0001-9893-6197</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>By Farzad Saffari 1,2,*,Sahar Zarei 1,3Orcid,Shobhit Kakaria 4Orcid,Enrique Bigné 4Orcid,Luis E. Bruni</t>
+          <t>Charles Stivale</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>_by_farzad_saffari__2PWuK4THxcLBD1-x6po7h</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>_charles_joseph_stivale_hIFjr8D0GQKZQAvOW-Mep</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0000-0001-9893-6197</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>stray orcid word</t>
+          <t>orcid embedded in name</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>cleaned in place</t>
+          <t>orcid api</t>
         </is>
       </c>
     </row>
@@ -2493,44 +2493,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-11-06T01:43:12Z</t>
+          <t>2026-02-06T09:02:13Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_126265', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1926']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_128016']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['droit', 'hist']</t>
+          <t>['manag', 'eco']</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>| orcid:0000-0002-3324-1324</t>
+          <t>| :0000-0001-8793-1200</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Patricia Zambrano</t>
+          <t>Patrick S Ward</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>_orcid__4txzOUqEmHR61Hw39r7En</t>
+          <t>_orcid__542hraj6pcdbIB_4_h9ws</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0000-0002-3324-1324</t>
+          <t>0000-0001-8793-1200</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -2549,44 +2549,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-06T09:02:13Z</t>
+          <t>2025-11-06T01:43:12Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_128016']</t>
+          <t>['ftifpriir:oai:ebrary.ifpri.org:p15738coll2_126265', 'ftifpriir:oai:ebrary.ifpri.org:p15738coll5_1926']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['manag', 'eco']</t>
+          <t>['droit', 'hist']</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>| :0000-0001-8793-1200</t>
+          <t>| orcid:0000-0002-3324-1324</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Patrick S Ward</t>
+          <t>Patricia Zambrano</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>_orcid__542hraj6pcdbIB_4_h9ws</t>
+          <t>_orcid__4txzOUqEmHR61Hw39r7En</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0000-0001-8793-1200</t>
+          <t>0000-0002-3324-1324</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>

--- a/data/output/authors_orcid_names_elastic.xlsx
+++ b/data/output/authors_orcid_names_elastic.xlsx
@@ -52,27 +52,27 @@
     <t>name_source</t>
   </si>
   <si>
+    <t>2026-08-22T09:46:33Z</t>
+  </si>
+  <si>
+    <t>2026-06-14T14:12:14Z</t>
+  </si>
+  <si>
+    <t>2026-08-10T23:52:04Z</t>
+  </si>
+  <si>
+    <t>2026-04-11T15:59:40Z</t>
+  </si>
+  <si>
     <t>2025-10-31T07:04:21Z</t>
   </si>
   <si>
-    <t>2026-08-22T09:46:33Z</t>
-  </si>
-  <si>
-    <t>2026-06-14T14:12:14Z</t>
-  </si>
-  <si>
-    <t>2026-04-11T15:59:40Z</t>
+    <t>2026-06-12T15:00:34Z</t>
   </si>
   <si>
     <t>2025-11-05T10:56:14Z</t>
   </si>
   <si>
-    <t>2026-08-10T23:52:04Z</t>
-  </si>
-  <si>
-    <t>2026-06-12T15:00:34Z</t>
-  </si>
-  <si>
     <t>2026-04-11T10:33:31Z</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>2026-05-18T15:43:07Z</t>
   </si>
   <si>
+    <t>2026-07-09T23:57:16Z</t>
+  </si>
+  <si>
     <t>2025-11-17T05:18:56Z</t>
   </si>
   <si>
-    <t>2026-07-09T23:57:16Z</t>
-  </si>
-  <si>
     <t>2025-11-05T03:45:27Z</t>
   </si>
   <si>
@@ -1273,30 +1273,30 @@
     <t>2026-06-07T11:00:21Z</t>
   </si>
   <si>
+    <t>['ftangliruskinfig:oai:figshare.com:article_29625350', 'ftbritmuseumfig:oai:figshare.com:article_29625350']</t>
+  </si>
+  <si>
+    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
+  </si>
+  <si>
+    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_01D8-V289']</t>
+  </si>
+  <si>
+    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XR71-ZM27']</t>
+  </si>
+  <si>
     <t>['50|dedup_wf_001::5ab4d3eee8a62e678110f1611761bb69']</t>
   </si>
   <si>
-    <t>['ftangliruskinfig:oai:figshare.com:article_29625350', 'ftbritmuseumfig:oai:figshare.com:article_29625350']</t>
-  </si>
-  <si>
-    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_TJK7-YD07']</t>
-  </si>
-  <si>
-    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XR71-ZM27']</t>
+    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XYK9-C767', 'ftpurdueunivpurr:https:__doi.org_10.4231_YSQA-C238', 'ftpurdueunivpurr:https:__doi.org_10.4231_39ZC-PV13', 'ftpurdueunivpurr:https:__doi.org_10.4231_5SC3-TF15', 'ftpurdueunivpurr:https:__doi.org_10.4231_DA5R-5M09', 'ftpurdueunivpurr:https:__doi.org_10.4231_Y0PA-B148', 'ftpurdueunivpurr:https:__doi.org_10.4231_SBGE-CG65', 'ftpurdueunivpurr:https:__doi.org_10.4231_26RX-W702', 'ftpurdueunivpurr:https:__doi.org_10.4231_MKD9-AT22', 'ftpurdueunivpurr:https:__doi.org_10.4231_ZY99-QF11', 'ftpurdueunivpurr:https:__doi.org_10.4231_TV7R-AG03', 'ftpurdueunivpurr:https:__doi.org_10.4231_7HAJ-WR33', 'ftpurdueunivpurr:https:__doi.org_10.4231_25NP-AF77', 'ftpurdueunivpurr:https:__doi.org_10.4231_JBFW-7V88', 'ftpurdueunivpurr:https:__doi.org_10.4231_VM0K-6320', 'ftpurdueunivpurr:https:__doi.org_10.4231_WXST-HY10', 'ftpurdueunivpurr:https:__doi.org_10.4231_TAVZ-T804', 'ftpurdueunivpurr:https:__doi.org_10.4231_ER7H-9390']</t>
+  </si>
+  <si>
+    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R76Q1V5Q']</t>
   </si>
   <si>
     <t>['ftzenodo:oai:zenodo.org:8081747']</t>
   </si>
   <si>
-    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_01D8-V289']</t>
-  </si>
-  <si>
-    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R76Q1V5Q']</t>
-  </si>
-  <si>
-    <t>['ftpurdueunivpurr:https:__doi.org_10.4231_XYK9-C767', 'ftpurdueunivpurr:https:__doi.org_10.4231_YSQA-C238', 'ftpurdueunivpurr:https:__doi.org_10.4231_39ZC-PV13', 'ftpurdueunivpurr:https:__doi.org_10.4231_5SC3-TF15', 'ftpurdueunivpurr:https:__doi.org_10.4231_DA5R-5M09', 'ftpurdueunivpurr:https:__doi.org_10.4231_Y0PA-B148', 'ftpurdueunivpurr:https:__doi.org_10.4231_SBGE-CG65', 'ftpurdueunivpurr:https:__doi.org_10.4231_26RX-W702', 'ftpurdueunivpurr:https:__doi.org_10.4231_MKD9-AT22', 'ftpurdueunivpurr:https:__doi.org_10.4231_ZY99-QF11', 'ftpurdueunivpurr:https:__doi.org_10.4231_TV7R-AG03', 'ftpurdueunivpurr:https:__doi.org_10.4231_7HAJ-WR33', 'ftpurdueunivpurr:https:__doi.org_10.4231_25NP-AF77', 'ftpurdueunivpurr:https:__doi.org_10.4231_JBFW-7V88', 'ftpurdueunivpurr:https:__doi.org_10.4231_VM0K-6320', 'ftpurdueunivpurr:https:__doi.org_10.4231_WXST-HY10', 'ftpurdueunivpurr:https:__doi.org_10.4231_TAVZ-T804', 'ftpurdueunivpurr:https:__doi.org_10.4231_ER7H-9390']</t>
-  </si>
-  <si>
     <t>['ftpurdueunivpurr:https:__doi.org_10.4231_R7MK6B49']</t>
   </si>
   <si>
@@ -2656,27 +2656,27 @@
     <t>['ftunivriojair:oai:portal.dialnet.es:doc_5bbc6926b750603269e8161c']</t>
   </si>
   <si>
+    <t>['edu', 'demo']</t>
+  </si>
+  <si>
+    <t>['demo', 'socio']</t>
+  </si>
+  <si>
+    <t>['geo', 'socio']</t>
+  </si>
+  <si>
     <t>['lang', 'hist']</t>
   </si>
   <si>
-    <t>['edu', 'demo']</t>
-  </si>
-  <si>
-    <t>['geo', 'socio']</t>
+    <t>['art', 'hist', 'musiq', 'archeo', 'scipo', 'phil']</t>
+  </si>
+  <si>
+    <t>['edu', 'socio']</t>
   </si>
   <si>
     <t>['psy', 'envir']</t>
   </si>
   <si>
-    <t>['demo', 'socio']</t>
-  </si>
-  <si>
-    <t>['edu', 'socio']</t>
-  </si>
-  <si>
-    <t>['art', 'hist', 'musiq', 'archeo', 'scipo', 'phil']</t>
-  </si>
-  <si>
     <t>['stat', 'litt']</t>
   </si>
   <si>
@@ -3472,30 +3472,30 @@
     <t>['litt', 'hist']</t>
   </si>
   <si>
+    <t>0000-0002-5658-6085 Al Saffar</t>
+  </si>
+  <si>
+    <t>Anne Lutomia, 0000-0001-6029-8783</t>
+  </si>
+  <si>
+    <t>Andrea Demaria, 0000-0002-5450-0444</t>
+  </si>
+  <si>
+    <t>Ana Morales, 0000-0001-6969-2883</t>
+  </si>
+  <si>
     <t>0000-0002-1588-0683</t>
   </si>
   <si>
-    <t>0000-0002-5658-6085 Al Saffar</t>
-  </si>
-  <si>
-    <t>Anne Lutomia, 0000-0001-6029-8783</t>
-  </si>
-  <si>
-    <t>Ana Morales, 0000-0001-6969-2883</t>
+    <t>Charles Joseph Stivale, 0000-0001-9893-6197</t>
+  </si>
+  <si>
+    <t>Chad Laux, 0000-0001-7445-2446</t>
   </si>
   <si>
     <t>by Farzad Saffari 1,2,*ORCID,Sahar Zarei 1,3ORCID,Shobhit Kakaria 4ORCID,Enrique Bigné 4ORCID,Luis E. Bruni</t>
   </si>
   <si>
-    <t>Andrea Demaria, 0000-0002-5450-0444</t>
-  </si>
-  <si>
-    <t>Chad Laux, 0000-0001-7445-2446</t>
-  </si>
-  <si>
-    <t>Charles Joseph Stivale, 0000-0001-9893-6197</t>
-  </si>
-  <si>
     <t>Corey S Seliger, 0000-0001-6100-3959</t>
   </si>
   <si>
@@ -4189,15 +4189,15 @@
     <t>0000-0002-0276-304X</t>
   </si>
   <si>
+    <t>0000-0001-5698-553X</t>
+  </si>
+  <si>
+    <t>0009-0004-7464-325X</t>
+  </si>
+  <si>
     <t>0000-0002-9750-287X</t>
   </si>
   <si>
-    <t>0000-0001-5698-553X</t>
-  </si>
-  <si>
-    <t>0009-0004-7464-325X</t>
-  </si>
-  <si>
     <t>Ye-Jee Jung, 0000-0002-8598-4023</t>
   </si>
   <si>
@@ -4738,30 +4738,30 @@
     <t>Arista, J.M. 0000-0001-9900-0104</t>
   </si>
   <si>
+    <t>May Ali Alsaffar</t>
+  </si>
+  <si>
+    <t>Anne Namatsi Lutomia</t>
+  </si>
+  <si>
+    <t>Andrea L. Demaria</t>
+  </si>
+  <si>
+    <t>Ana Morales</t>
+  </si>
+  <si>
     <t>Thiago Lima Nicodemo</t>
   </si>
   <si>
-    <t>May Ali Alsaffar</t>
-  </si>
-  <si>
-    <t>Anne Namatsi Lutomia</t>
-  </si>
-  <si>
-    <t>Ana Morales</t>
+    <t>Charles Stivale</t>
+  </si>
+  <si>
+    <t>Chad Laux</t>
   </si>
   <si>
     <t>By Farzad Saffari 1,2,*,Sahar Zarei 1,3Orcid,Shobhit Kakaria 4Orcid,Enrique Bigné 4Orcid,Luis E. Bruni</t>
   </si>
   <si>
-    <t>Andrea L. Demaria</t>
-  </si>
-  <si>
-    <t>Chad Laux</t>
-  </si>
-  <si>
-    <t>Charles Stivale</t>
-  </si>
-  <si>
     <t>Corey Seliger</t>
   </si>
   <si>
@@ -5452,15 +5452,15 @@
     <t>Dominika Schmidtová</t>
   </si>
   <si>
+    <t>Akimasa Takahashi</t>
+  </si>
+  <si>
+    <t>Ariel Natalo-Lifton</t>
+  </si>
+  <si>
     <t>Lindy Willmott</t>
   </si>
   <si>
-    <t>Akimasa Takahashi</t>
-  </si>
-  <si>
-    <t>Ariel Natalo-Lifton</t>
-  </si>
-  <si>
     <t>Ye-Jee Jung</t>
   </si>
   <si>
@@ -5953,30 +5953,30 @@
     <t>Javier Martín Arista</t>
   </si>
   <si>
+    <t>_al_saffar_91YLQAAzbumMeER42sOag</t>
+  </si>
+  <si>
+    <t>_anne_lutomia_qPc5d120hLDhlDGt0zvkh</t>
+  </si>
+  <si>
+    <t>_andrea_demaria_BeJ9VyDol6i1hMQ5Ck9sm</t>
+  </si>
+  <si>
+    <t>_ana_morales_3mGc2R6NYalGGGePNQM5k</t>
+  </si>
+  <si>
     <t>__yGdlcy3e2m0M8R9H4gLU6</t>
   </si>
   <si>
-    <t>_al_saffar_91YLQAAzbumMeER42sOag</t>
-  </si>
-  <si>
-    <t>_anne_lutomia_qPc5d120hLDhlDGt0zvkh</t>
-  </si>
-  <si>
-    <t>_ana_morales_3mGc2R6NYalGGGePNQM5k</t>
+    <t>_charles_joseph_stivale_hIFjr8D0GQKZQAvOW-Mep</t>
+  </si>
+  <si>
+    <t>_chad_laux_P8HwWOySU2u_ccVtBC_FL</t>
   </si>
   <si>
     <t>_by_farzad_saffari__2PWuK4THxcLBD1-x6po7h</t>
   </si>
   <si>
-    <t>_andrea_demaria_BeJ9VyDol6i1hMQ5Ck9sm</t>
-  </si>
-  <si>
-    <t>_chad_laux_P8HwWOySU2u_ccVtBC_FL</t>
-  </si>
-  <si>
-    <t>_charles_joseph_stivale_hIFjr8D0GQKZQAvOW-Mep</t>
-  </si>
-  <si>
     <t>_corey_s_seliger_Fa5tC9R7eFp_X_pAfxOfG</t>
   </si>
   <si>
@@ -6724,15 +6724,15 @@
     <t>_x_yz8X64ISSmUIngsripiRc</t>
   </si>
   <si>
+    <t>_x_zUp1AyCySThoMIKD8uXDn</t>
+  </si>
+  <si>
+    <t>_x_zn9SRWUkDsNMERkZ0zf-3</t>
+  </si>
+  <si>
     <t>_x_zUKEbOwSiFrPmpVsiOIRx</t>
   </si>
   <si>
-    <t>_x_zUp1AyCySThoMIKD8uXDn</t>
-  </si>
-  <si>
-    <t>_x_zn9SRWUkDsNMERkZ0zf-3</t>
-  </si>
-  <si>
     <t>_ye_jee_jung_6xrPPRiwnEAVFqHr2EpVi</t>
   </si>
   <si>
@@ -7420,12 +7420,12 @@
     <t>aphiwe_orcid_mpateni_U7G0mgYlFbsHlvrPz1W3o</t>
   </si>
   <si>
+    <t>aphiwe_orcid_nguma_QuZ8cVOrLqBXL1bZb1mra</t>
+  </si>
+  <si>
     <t>ardeshir_bazrkar_orcid_NKKokyVifTJGxmSSMkQKE</t>
   </si>
   <si>
-    <t>aphiwe_orcid_nguma_QuZ8cVOrLqBXL1bZb1mra</t>
-  </si>
-  <si>
     <t>araceli_jaimes_arredondo__q98UfRB3NvLLUB7x4Etqy</t>
   </si>
   <si>
@@ -7459,18 +7459,18 @@
     <t>0000-0001-6029-8783</t>
   </si>
   <si>
+    <t>0000-0002-5450-0444</t>
+  </si>
+  <si>
     <t>0000-0001-6969-2883</t>
   </si>
   <si>
-    <t>0000-0002-5450-0444</t>
+    <t>0000-0001-9893-6197</t>
   </si>
   <si>
     <t>0000-0001-7445-2446</t>
   </si>
   <si>
-    <t>0000-0001-9893-6197</t>
-  </si>
-  <si>
     <t>0000-0001-6100-3959</t>
   </si>
   <si>
@@ -8281,10 +8281,10 @@
     <t>0000-0001-9900-0104</t>
   </si>
   <si>
+    <t>orcid embedded in name</t>
+  </si>
+  <si>
     <t>orcid only</t>
-  </si>
-  <si>
-    <t>orcid embedded in name</t>
   </si>
   <si>
     <t>stray orcid word</t>
@@ -8677,7 +8677,7 @@
         <v>880</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>1152</v>
@@ -8689,10 +8689,10 @@
         <v>1979</v>
       </c>
       <c r="H2" t="s">
-        <v>1152</v>
+        <v>2479</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         <v>420</v>
       </c>
       <c r="C3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>1153</v>
@@ -8727,16 +8727,16 @@
         <v>1980</v>
       </c>
       <c r="H3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L3" t="s">
         <v>2758</v>
@@ -8753,7 +8753,7 @@
         <v>881</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>1154</v>
@@ -8765,7 +8765,7 @@
         <v>1981</v>
       </c>
       <c r="H4" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -8774,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L4" t="s">
         <v>2758</v>
@@ -8803,7 +8803,7 @@
         <v>1982</v>
       </c>
       <c r="H5" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -8812,7 +8812,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L5" t="s">
         <v>2758</v>
@@ -8829,7 +8829,7 @@
         <v>883</v>
       </c>
       <c r="D6">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
         <v>1156</v>
@@ -8840,6 +8840,9 @@
       <c r="G6" t="s">
         <v>1983</v>
       </c>
+      <c r="H6" t="s">
+        <v>1156</v>
+      </c>
       <c r="I6">
         <v>1</v>
       </c>
@@ -8847,10 +8850,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="L6" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -8864,7 +8867,7 @@
         <v>884</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>1157</v>
@@ -8876,16 +8879,16 @@
         <v>1984</v>
       </c>
       <c r="H7" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L7" t="s">
         <v>2758</v>
@@ -8893,7 +8896,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>425</v>
@@ -8914,7 +8917,7 @@
         <v>1985</v>
       </c>
       <c r="H8" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -8923,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L8" t="s">
         <v>2758</v>
@@ -8940,7 +8943,7 @@
         <v>886</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>1159</v>
@@ -8951,25 +8954,22 @@
       <c r="G9" t="s">
         <v>1986</v>
       </c>
-      <c r="H9" t="s">
-        <v>2484</v>
-      </c>
       <c r="I9">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="L9" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>427</v>
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L10" t="s">
         <v>2758</v>
@@ -9007,13 +9007,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C11" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D11">
         <v>35</v>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L11" t="s">
         <v>2758</v>
@@ -9075,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L12" t="s">
         <v>2758</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L13" t="s">
         <v>2758</v>
@@ -9151,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L14" t="s">
         <v>2758</v>
@@ -9189,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L15" t="s">
         <v>2758</v>
@@ -9227,7 +9227,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L16" t="s">
         <v>2758</v>
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L17" t="s">
         <v>2758</v>
@@ -9303,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L18" t="s">
         <v>2758</v>
@@ -9341,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L19" t="s">
         <v>2758</v>
@@ -9379,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L20" t="s">
         <v>2758</v>
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L21" t="s">
         <v>2758</v>
@@ -9428,10 +9428,10 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C22" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D22">
         <v>43</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L22" t="s">
         <v>2758</v>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
         <v>437</v>
@@ -9493,7 +9493,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L23" t="s">
         <v>2758</v>
@@ -9531,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L24" t="s">
         <v>2758</v>
@@ -9542,10 +9542,10 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C25" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D25">
         <v>38</v>
@@ -9569,7 +9569,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L25" t="s">
         <v>2758</v>
@@ -9607,7 +9607,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L26" t="s">
         <v>2758</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L27" t="s">
         <v>2758</v>
@@ -9683,7 +9683,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L28" t="s">
         <v>2758</v>
@@ -9721,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L29" t="s">
         <v>2758</v>
@@ -9759,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L30" t="s">
         <v>2758</v>
@@ -9797,7 +9797,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L31" t="s">
         <v>2758</v>
@@ -9835,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L32" t="s">
         <v>2758</v>
@@ -9873,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L33" t="s">
         <v>2758</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L34" t="s">
         <v>2758</v>
@@ -9949,7 +9949,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L35" t="s">
         <v>2758</v>
@@ -9960,10 +9960,10 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C36" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D36">
         <v>40</v>
@@ -9987,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L36" t="s">
         <v>2758</v>
@@ -10025,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L37" t="s">
         <v>2758</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L38" t="s">
         <v>2758</v>
@@ -10101,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L39" t="s">
         <v>2758</v>
@@ -10139,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L40" t="s">
         <v>2758</v>
@@ -10177,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L41" t="s">
         <v>2758</v>
@@ -10215,7 +10215,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L42" t="s">
         <v>2758</v>
@@ -10253,7 +10253,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L43" t="s">
         <v>2758</v>
@@ -10291,7 +10291,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L44" t="s">
         <v>2758</v>
@@ -10329,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L45" t="s">
         <v>2758</v>
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L46" t="s">
         <v>2758</v>
@@ -10405,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L47" t="s">
         <v>2758</v>
@@ -10443,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L48" t="s">
         <v>2758</v>
@@ -10481,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L49" t="s">
         <v>2758</v>
@@ -10519,7 +10519,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L50" t="s">
         <v>2758</v>
@@ -10557,7 +10557,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L51" t="s">
         <v>2758</v>
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L52" t="s">
         <v>2758</v>
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L53" t="s">
         <v>2758</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L54" t="s">
         <v>2758</v>
@@ -10709,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L55" t="s">
         <v>2758</v>
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L56" t="s">
         <v>2758</v>
@@ -10785,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L57" t="s">
         <v>2758</v>
@@ -10823,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L58" t="s">
         <v>2758</v>
@@ -10861,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L59" t="s">
         <v>2758</v>
@@ -10899,7 +10899,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L60" t="s">
         <v>2758</v>
@@ -10937,7 +10937,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L61" t="s">
         <v>2758</v>
@@ -10975,7 +10975,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L62" t="s">
         <v>2758</v>
@@ -11013,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L63" t="s">
         <v>2758</v>
@@ -11051,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L64" t="s">
         <v>2758</v>
@@ -11089,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L65" t="s">
         <v>2758</v>
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L66" t="s">
         <v>2758</v>
@@ -11165,7 +11165,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L67" t="s">
         <v>2758</v>
@@ -11203,7 +11203,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L68" t="s">
         <v>2758</v>
@@ -11241,7 +11241,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L69" t="s">
         <v>2758</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L70" t="s">
         <v>2758</v>
@@ -11317,7 +11317,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L71" t="s">
         <v>2758</v>
@@ -11355,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L72" t="s">
         <v>2758</v>
@@ -11393,7 +11393,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L73" t="s">
         <v>2758</v>
@@ -11431,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L74" t="s">
         <v>2758</v>
@@ -11469,7 +11469,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L75" t="s">
         <v>2758</v>
@@ -11507,7 +11507,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L76" t="s">
         <v>2758</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L77" t="s">
         <v>2758</v>
@@ -11583,7 +11583,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L78" t="s">
         <v>2758</v>
@@ -11621,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L79" t="s">
         <v>2758</v>
@@ -11659,7 +11659,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L80" t="s">
         <v>2758</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L81" t="s">
         <v>2758</v>
@@ -11735,7 +11735,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L82" t="s">
         <v>2758</v>
@@ -11773,7 +11773,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L83" t="s">
         <v>2758</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L84" t="s">
         <v>2758</v>
@@ -11849,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L85" t="s">
         <v>2758</v>
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L86" t="s">
         <v>2758</v>
@@ -11925,7 +11925,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L87" t="s">
         <v>2758</v>
@@ -11963,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L88" t="s">
         <v>2758</v>
@@ -12001,7 +12001,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L89" t="s">
         <v>2758</v>
@@ -12039,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L90" t="s">
         <v>2758</v>
@@ -12077,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L91" t="s">
         <v>2758</v>
@@ -12115,7 +12115,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L92" t="s">
         <v>2758</v>
@@ -12153,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L93" t="s">
         <v>2758</v>
@@ -12191,7 +12191,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L94" t="s">
         <v>2758</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L95" t="s">
         <v>2758</v>
@@ -12267,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L96" t="s">
         <v>2758</v>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L97" t="s">
         <v>2758</v>
@@ -12343,7 +12343,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L98" t="s">
         <v>2758</v>
@@ -12381,7 +12381,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L99" t="s">
         <v>2758</v>
@@ -12419,7 +12419,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L100" t="s">
         <v>2758</v>
@@ -12457,7 +12457,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L101" t="s">
         <v>2758</v>
@@ -12495,7 +12495,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L102" t="s">
         <v>2758</v>
@@ -12533,7 +12533,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L103" t="s">
         <v>2758</v>
@@ -12571,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L104" t="s">
         <v>2758</v>
@@ -12609,7 +12609,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L105" t="s">
         <v>2758</v>
@@ -12647,7 +12647,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L106" t="s">
         <v>2758</v>
@@ -12685,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L107" t="s">
         <v>2758</v>
@@ -12723,7 +12723,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L108" t="s">
         <v>2758</v>
@@ -12761,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L109" t="s">
         <v>2758</v>
@@ -12799,7 +12799,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L110" t="s">
         <v>2758</v>
@@ -12837,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L111" t="s">
         <v>2758</v>
@@ -12875,7 +12875,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L112" t="s">
         <v>2758</v>
@@ -12913,7 +12913,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L113" t="s">
         <v>2758</v>
@@ -12951,7 +12951,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L114" t="s">
         <v>2758</v>
@@ -12989,7 +12989,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L115" t="s">
         <v>2758</v>
@@ -13027,7 +13027,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L116" t="s">
         <v>2758</v>
@@ -13065,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L117" t="s">
         <v>2758</v>
@@ -13103,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L118" t="s">
         <v>2758</v>
@@ -13141,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L119" t="s">
         <v>2758</v>
@@ -13179,7 +13179,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L120" t="s">
         <v>2758</v>
@@ -13217,7 +13217,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L121" t="s">
         <v>2758</v>
@@ -13255,7 +13255,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L122" t="s">
         <v>2758</v>
@@ -13293,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L123" t="s">
         <v>2758</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L124" t="s">
         <v>2758</v>
@@ -13369,7 +13369,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L125" t="s">
         <v>2758</v>
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L126" t="s">
         <v>2758</v>
@@ -13445,7 +13445,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L127" t="s">
         <v>2758</v>
@@ -13483,7 +13483,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L128" t="s">
         <v>2758</v>
@@ -13521,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L129" t="s">
         <v>2758</v>
@@ -13559,7 +13559,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L130" t="s">
         <v>2758</v>
@@ -13597,7 +13597,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L131" t="s">
         <v>2758</v>
@@ -13611,7 +13611,7 @@
         <v>538</v>
       </c>
       <c r="C132" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="D132">
         <v>19</v>
@@ -13635,7 +13635,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L132" t="s">
         <v>2758</v>
@@ -13673,7 +13673,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L133" t="s">
         <v>2758</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L134" t="s">
         <v>2758</v>
@@ -13749,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L135" t="s">
         <v>2758</v>
@@ -13787,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L136" t="s">
         <v>2758</v>
@@ -13825,7 +13825,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L137" t="s">
         <v>2758</v>
@@ -13863,7 +13863,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L138" t="s">
         <v>2758</v>
@@ -13901,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L139" t="s">
         <v>2758</v>
@@ -13939,7 +13939,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L140" t="s">
         <v>2758</v>
@@ -13977,7 +13977,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L141" t="s">
         <v>2758</v>
@@ -14015,7 +14015,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L142" t="s">
         <v>2758</v>
@@ -14053,7 +14053,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L143" t="s">
         <v>2758</v>
@@ -14091,7 +14091,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L144" t="s">
         <v>2758</v>
@@ -14129,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L145" t="s">
         <v>2758</v>
@@ -14167,7 +14167,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L146" t="s">
         <v>2758</v>
@@ -14205,7 +14205,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L147" t="s">
         <v>2758</v>
@@ -14243,7 +14243,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L148" t="s">
         <v>2758</v>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L149" t="s">
         <v>2758</v>
@@ -14319,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L150" t="s">
         <v>2758</v>
@@ -14357,7 +14357,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L151" t="s">
         <v>2758</v>
@@ -14395,7 +14395,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L152" t="s">
         <v>2758</v>
@@ -14433,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L153" t="s">
         <v>2758</v>
@@ -14471,7 +14471,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L154" t="s">
         <v>2758</v>
@@ -14509,7 +14509,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L155" t="s">
         <v>2758</v>
@@ -14547,7 +14547,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L156" t="s">
         <v>2758</v>
@@ -14585,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L157" t="s">
         <v>2758</v>
@@ -14623,7 +14623,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L158" t="s">
         <v>2758</v>
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L159" t="s">
         <v>2758</v>
@@ -14699,7 +14699,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L160" t="s">
         <v>2758</v>
@@ -14737,7 +14737,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L161" t="s">
         <v>2758</v>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L162" t="s">
         <v>2758</v>
@@ -14813,7 +14813,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L163" t="s">
         <v>2758</v>
@@ -14851,7 +14851,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L164" t="s">
         <v>2758</v>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L165" t="s">
         <v>2758</v>
@@ -14927,7 +14927,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L166" t="s">
         <v>2758</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L167" t="s">
         <v>2758</v>
@@ -15003,7 +15003,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L168" t="s">
         <v>2758</v>
@@ -15041,7 +15041,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L169" t="s">
         <v>2758</v>
@@ -15079,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L170" t="s">
         <v>2758</v>
@@ -15117,7 +15117,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L171" t="s">
         <v>2758</v>
@@ -15155,7 +15155,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L172" t="s">
         <v>2758</v>
@@ -15193,7 +15193,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L173" t="s">
         <v>2758</v>
@@ -15231,7 +15231,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L174" t="s">
         <v>2758</v>
@@ -15269,7 +15269,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L175" t="s">
         <v>2758</v>
@@ -15307,7 +15307,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L176" t="s">
         <v>2758</v>
@@ -15345,7 +15345,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L177" t="s">
         <v>2758</v>
@@ -15383,7 +15383,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L178" t="s">
         <v>2758</v>
@@ -15421,7 +15421,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L179" t="s">
         <v>2758</v>
@@ -15459,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L180" t="s">
         <v>2758</v>
@@ -15497,7 +15497,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L181" t="s">
         <v>2758</v>
@@ -15535,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L182" t="s">
         <v>2758</v>
@@ -15573,7 +15573,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L183" t="s">
         <v>2758</v>
@@ -15611,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L184" t="s">
         <v>2758</v>
@@ -15649,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L185" t="s">
         <v>2758</v>
@@ -15687,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L186" t="s">
         <v>2758</v>
@@ -15725,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L187" t="s">
         <v>2758</v>
@@ -15763,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L188" t="s">
         <v>2758</v>
@@ -15801,7 +15801,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L189" t="s">
         <v>2758</v>
@@ -15839,7 +15839,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L190" t="s">
         <v>2758</v>
@@ -15877,7 +15877,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L191" t="s">
         <v>2758</v>
@@ -15915,7 +15915,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L192" t="s">
         <v>2758</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L193" t="s">
         <v>2758</v>
@@ -15991,7 +15991,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L194" t="s">
         <v>2758</v>
@@ -16029,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L195" t="s">
         <v>2758</v>
@@ -16067,7 +16067,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L196" t="s">
         <v>2758</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L197" t="s">
         <v>2758</v>
@@ -16143,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L198" t="s">
         <v>2758</v>
@@ -16181,7 +16181,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L199" t="s">
         <v>2758</v>
@@ -16219,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L200" t="s">
         <v>2758</v>
@@ -16257,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L201" t="s">
         <v>2758</v>
@@ -16295,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L202" t="s">
         <v>2758</v>
@@ -16333,7 +16333,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L203" t="s">
         <v>2758</v>
@@ -16371,7 +16371,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L204" t="s">
         <v>2758</v>
@@ -16409,7 +16409,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L205" t="s">
         <v>2758</v>
@@ -16447,7 +16447,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L206" t="s">
         <v>2758</v>
@@ -16485,7 +16485,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L207" t="s">
         <v>2758</v>
@@ -16523,7 +16523,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L208" t="s">
         <v>2758</v>
@@ -16561,7 +16561,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L209" t="s">
         <v>2758</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L210" t="s">
         <v>2758</v>
@@ -16637,7 +16637,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L211" t="s">
         <v>2758</v>
@@ -16675,7 +16675,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L212" t="s">
         <v>2758</v>
@@ -16713,7 +16713,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L213" t="s">
         <v>2758</v>
@@ -16751,7 +16751,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L214" t="s">
         <v>2758</v>
@@ -16789,7 +16789,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L215" t="s">
         <v>2758</v>
@@ -16827,7 +16827,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L216" t="s">
         <v>2758</v>
@@ -16865,7 +16865,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L217" t="s">
         <v>2758</v>
@@ -16903,7 +16903,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L218" t="s">
         <v>2758</v>
@@ -16941,7 +16941,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L219" t="s">
         <v>2758</v>
@@ -16979,7 +16979,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L220" t="s">
         <v>2758</v>
@@ -17017,7 +17017,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L221" t="s">
         <v>2758</v>
@@ -17055,7 +17055,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L222" t="s">
         <v>2758</v>
@@ -17093,7 +17093,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L223" t="s">
         <v>2758</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L224" t="s">
         <v>2758</v>
@@ -17169,7 +17169,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L225" t="s">
         <v>2758</v>
@@ -17207,7 +17207,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L226" t="s">
         <v>2758</v>
@@ -17245,7 +17245,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L227" t="s">
         <v>2758</v>
@@ -17283,7 +17283,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L228" t="s">
         <v>2758</v>
@@ -17321,7 +17321,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L229" t="s">
         <v>2758</v>
@@ -17359,7 +17359,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L230" t="s">
         <v>2758</v>
@@ -17397,7 +17397,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L231" t="s">
         <v>2758</v>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L232" t="s">
         <v>2758</v>
@@ -17473,7 +17473,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L233" t="s">
         <v>2758</v>
@@ -17511,7 +17511,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L234" t="s">
         <v>2758</v>
@@ -17549,7 +17549,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L235" t="s">
         <v>2758</v>
@@ -17587,7 +17587,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L236" t="s">
         <v>2758</v>
@@ -17625,7 +17625,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L237" t="s">
         <v>2758</v>
@@ -17663,7 +17663,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L238" t="s">
         <v>2758</v>
@@ -17701,7 +17701,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L239" t="s">
         <v>2758</v>
@@ -17739,7 +17739,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L240" t="s">
         <v>2758</v>
@@ -17777,7 +17777,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L241" t="s">
         <v>2758</v>
@@ -17815,7 +17815,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L242" t="s">
         <v>2758</v>
@@ -17853,7 +17853,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L243" t="s">
         <v>2758</v>
@@ -17891,7 +17891,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L244" t="s">
         <v>2758</v>
@@ -17929,7 +17929,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L245" t="s">
         <v>2758</v>
@@ -17943,7 +17943,7 @@
         <v>538</v>
       </c>
       <c r="C246" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="D246">
         <v>19</v>
@@ -17967,7 +17967,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L246" t="s">
         <v>2758</v>
@@ -18005,7 +18005,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L247" t="s">
         <v>2758</v>
@@ -18043,7 +18043,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L248" t="s">
         <v>2758</v>
@@ -18081,7 +18081,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L249" t="s">
         <v>2758</v>
@@ -18119,7 +18119,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L250" t="s">
         <v>2758</v>
@@ -18157,7 +18157,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L251" t="s">
         <v>2758</v>
@@ -18195,7 +18195,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L252" t="s">
         <v>2758</v>
@@ -18233,7 +18233,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L253" t="s">
         <v>2758</v>
@@ -18271,7 +18271,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L254" t="s">
         <v>2758</v>
@@ -18309,7 +18309,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L255" t="s">
         <v>2758</v>
@@ -18347,7 +18347,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L256" t="s">
         <v>2758</v>
@@ -18385,7 +18385,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L257" t="s">
         <v>2758</v>
@@ -18423,7 +18423,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L258" t="s">
         <v>2758</v>
@@ -18431,13 +18431,13 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B259" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="C259" t="s">
-        <v>1035</v>
+        <v>987</v>
       </c>
       <c r="D259">
         <v>19</v>
@@ -18461,7 +18461,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L259" t="s">
         <v>2758</v>
@@ -18469,13 +18469,13 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B260" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C260" t="s">
-        <v>987</v>
+        <v>1044</v>
       </c>
       <c r="D260">
         <v>19</v>
@@ -18499,7 +18499,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L260" t="s">
         <v>2758</v>
@@ -18507,13 +18507,13 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B261" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="C261" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="D261">
         <v>19</v>
@@ -18537,7 +18537,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L261" t="s">
         <v>2758</v>
@@ -18575,7 +18575,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L262" t="s">
         <v>2758</v>
@@ -18613,7 +18613,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L263" t="s">
         <v>2758</v>
@@ -18651,7 +18651,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L264" t="s">
         <v>2758</v>
@@ -18689,7 +18689,7 @@
         <v>0</v>
       </c>
       <c r="K265" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L265" t="s">
         <v>2758</v>
@@ -18727,7 +18727,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L266" t="s">
         <v>2758</v>
@@ -18765,7 +18765,7 @@
         <v>0</v>
       </c>
       <c r="K267" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L267" t="s">
         <v>2758</v>
@@ -18803,7 +18803,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L268" t="s">
         <v>2758</v>
@@ -18841,7 +18841,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L269" t="s">
         <v>2758</v>
@@ -18879,7 +18879,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L270" t="s">
         <v>2758</v>
@@ -18917,7 +18917,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L271" t="s">
         <v>2758</v>
@@ -18955,7 +18955,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L272" t="s">
         <v>2758</v>
@@ -18993,7 +18993,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L273" t="s">
         <v>2758</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L274" t="s">
         <v>2758</v>
@@ -19069,7 +19069,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L275" t="s">
         <v>2758</v>
@@ -19107,7 +19107,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L276" t="s">
         <v>2758</v>
@@ -19145,7 +19145,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L277" t="s">
         <v>2758</v>
@@ -19183,7 +19183,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L278" t="s">
         <v>2758</v>
@@ -19221,7 +19221,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L279" t="s">
         <v>2758</v>
@@ -19259,7 +19259,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L280" t="s">
         <v>2758</v>
@@ -19297,7 +19297,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L281" t="s">
         <v>2758</v>
@@ -19335,7 +19335,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L282" t="s">
         <v>2758</v>
@@ -19373,7 +19373,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L283" t="s">
         <v>2758</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L284" t="s">
         <v>2758</v>
@@ -19449,7 +19449,7 @@
         <v>0</v>
       </c>
       <c r="K285" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L285" t="s">
         <v>2758</v>
@@ -19487,7 +19487,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L286" t="s">
         <v>2758</v>
@@ -19525,7 +19525,7 @@
         <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L287" t="s">
         <v>2758</v>
@@ -19563,7 +19563,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L288" t="s">
         <v>2758</v>
@@ -19601,7 +19601,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L289" t="s">
         <v>2758</v>
@@ -19639,7 +19639,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L290" t="s">
         <v>2758</v>
@@ -19677,7 +19677,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L291" t="s">
         <v>2758</v>
@@ -19715,7 +19715,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L292" t="s">
         <v>2758</v>
@@ -19753,7 +19753,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L293" t="s">
         <v>2758</v>
@@ -19791,7 +19791,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L294" t="s">
         <v>2758</v>
@@ -19829,7 +19829,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L295" t="s">
         <v>2758</v>
@@ -19867,7 +19867,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L296" t="s">
         <v>2758</v>
@@ -19905,7 +19905,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L297" t="s">
         <v>2758</v>
@@ -19943,7 +19943,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L298" t="s">
         <v>2758</v>
@@ -19981,7 +19981,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L299" t="s">
         <v>2758</v>
@@ -20019,7 +20019,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L300" t="s">
         <v>2758</v>
@@ -20057,7 +20057,7 @@
         <v>0</v>
       </c>
       <c r="K301" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L301" t="s">
         <v>2758</v>
@@ -20095,7 +20095,7 @@
         <v>0</v>
       </c>
       <c r="K302" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L302" t="s">
         <v>2758</v>
@@ -20133,7 +20133,7 @@
         <v>0</v>
       </c>
       <c r="K303" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L303" t="s">
         <v>2758</v>
@@ -20171,7 +20171,7 @@
         <v>0</v>
       </c>
       <c r="K304" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L304" t="s">
         <v>2758</v>
@@ -20209,7 +20209,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L305" t="s">
         <v>2758</v>
@@ -20247,7 +20247,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L306" t="s">
         <v>2758</v>
@@ -20285,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L307" t="s">
         <v>2758</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="K308" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L308" t="s">
         <v>2758</v>
@@ -20361,7 +20361,7 @@
         <v>0</v>
       </c>
       <c r="K309" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L309" t="s">
         <v>2758</v>
@@ -20399,7 +20399,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L310" t="s">
         <v>2758</v>
@@ -20437,7 +20437,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L311" t="s">
         <v>2758</v>
@@ -20475,7 +20475,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L312" t="s">
         <v>2758</v>
@@ -20513,7 +20513,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L313" t="s">
         <v>2758</v>
@@ -20551,7 +20551,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L314" t="s">
         <v>2758</v>
@@ -20589,7 +20589,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L315" t="s">
         <v>2758</v>
@@ -20627,7 +20627,7 @@
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L316" t="s">
         <v>2758</v>
@@ -20665,7 +20665,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L317" t="s">
         <v>2758</v>
@@ -20703,7 +20703,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L318" t="s">
         <v>2758</v>
@@ -20741,7 +20741,7 @@
         <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L319" t="s">
         <v>2758</v>
@@ -20779,7 +20779,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L320" t="s">
         <v>2758</v>
@@ -20817,7 +20817,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L321" t="s">
         <v>2758</v>
@@ -20855,7 +20855,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L322" t="s">
         <v>2758</v>
@@ -20893,7 +20893,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L323" t="s">
         <v>2758</v>
@@ -20931,7 +20931,7 @@
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L324" t="s">
         <v>2758</v>
@@ -20969,7 +20969,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L325" t="s">
         <v>2758</v>
@@ -21007,7 +21007,7 @@
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L326" t="s">
         <v>2758</v>
@@ -21021,7 +21021,7 @@
         <v>720</v>
       </c>
       <c r="C327" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="D327">
         <v>43</v>
@@ -21045,7 +21045,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L327" t="s">
         <v>2758</v>
@@ -21083,7 +21083,7 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L328" t="s">
         <v>2758</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L329" t="s">
         <v>2758</v>
@@ -21159,7 +21159,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L330" t="s">
         <v>2758</v>
@@ -21197,7 +21197,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L331" t="s">
         <v>2758</v>
@@ -21235,7 +21235,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L332" t="s">
         <v>2758</v>
@@ -21273,7 +21273,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L333" t="s">
         <v>2758</v>
@@ -21311,7 +21311,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L334" t="s">
         <v>2758</v>
@@ -21349,7 +21349,7 @@
         <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L335" t="s">
         <v>2758</v>
@@ -21387,7 +21387,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L336" t="s">
         <v>2758</v>
@@ -21425,7 +21425,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L337" t="s">
         <v>2758</v>
@@ -21463,7 +21463,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L338" t="s">
         <v>2758</v>
@@ -21501,7 +21501,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L339" t="s">
         <v>2758</v>
@@ -21539,7 +21539,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L340" t="s">
         <v>2758</v>
@@ -21577,7 +21577,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L341" t="s">
         <v>2758</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="K342" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L342" t="s">
         <v>2758</v>
@@ -21653,7 +21653,7 @@
         <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L343" t="s">
         <v>2758</v>
@@ -21691,7 +21691,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L344" t="s">
         <v>2758</v>
@@ -21729,7 +21729,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L345" t="s">
         <v>2758</v>
@@ -21767,7 +21767,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L346" t="s">
         <v>2758</v>
@@ -21805,7 +21805,7 @@
         <v>0</v>
       </c>
       <c r="K347" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L347" t="s">
         <v>2758</v>
@@ -21843,7 +21843,7 @@
         <v>0</v>
       </c>
       <c r="K348" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L348" t="s">
         <v>2758</v>
@@ -21881,7 +21881,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L349" t="s">
         <v>2758</v>
@@ -21919,7 +21919,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L350" t="s">
         <v>2758</v>
@@ -21957,7 +21957,7 @@
         <v>0</v>
       </c>
       <c r="K351" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L351" t="s">
         <v>2758</v>
@@ -21995,7 +21995,7 @@
         <v>0</v>
       </c>
       <c r="K352" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L352" t="s">
         <v>2758</v>
@@ -22033,7 +22033,7 @@
         <v>0</v>
       </c>
       <c r="K353" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L353" t="s">
         <v>2758</v>
@@ -22071,7 +22071,7 @@
         <v>0</v>
       </c>
       <c r="K354" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L354" t="s">
         <v>2758</v>
@@ -22109,7 +22109,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L355" t="s">
         <v>2758</v>
@@ -22147,7 +22147,7 @@
         <v>0</v>
       </c>
       <c r="K356" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L356" t="s">
         <v>2758</v>
@@ -22185,7 +22185,7 @@
         <v>0</v>
       </c>
       <c r="K357" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L357" t="s">
         <v>2758</v>
@@ -22223,7 +22223,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L358" t="s">
         <v>2758</v>
@@ -22261,7 +22261,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L359" t="s">
         <v>2758</v>
@@ -22299,7 +22299,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L360" t="s">
         <v>2758</v>
@@ -22337,7 +22337,7 @@
         <v>0</v>
       </c>
       <c r="K361" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L361" t="s">
         <v>2758</v>
@@ -22375,7 +22375,7 @@
         <v>0</v>
       </c>
       <c r="K362" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L362" t="s">
         <v>2758</v>
@@ -22413,7 +22413,7 @@
         <v>0</v>
       </c>
       <c r="K363" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L363" t="s">
         <v>2758</v>
@@ -22451,7 +22451,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L364" t="s">
         <v>2758</v>
@@ -22489,7 +22489,7 @@
         <v>0</v>
       </c>
       <c r="K365" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L365" t="s">
         <v>2758</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="K366" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L366" t="s">
         <v>2758</v>
@@ -22565,7 +22565,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L367" t="s">
         <v>2758</v>
@@ -22603,7 +22603,7 @@
         <v>0</v>
       </c>
       <c r="K368" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L368" t="s">
         <v>2758</v>
@@ -22641,7 +22641,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L369" t="s">
         <v>2758</v>
@@ -22679,7 +22679,7 @@
         <v>0</v>
       </c>
       <c r="K370" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L370" t="s">
         <v>2758</v>
@@ -22717,7 +22717,7 @@
         <v>0</v>
       </c>
       <c r="K371" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L371" t="s">
         <v>2758</v>
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="K372" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L372" t="s">
         <v>2758</v>
@@ -22793,7 +22793,7 @@
         <v>0</v>
       </c>
       <c r="K373" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L373" t="s">
         <v>2758</v>
@@ -22831,7 +22831,7 @@
         <v>0</v>
       </c>
       <c r="K374" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L374" t="s">
         <v>2758</v>
@@ -22869,7 +22869,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L375" t="s">
         <v>2758</v>
@@ -22907,7 +22907,7 @@
         <v>0</v>
       </c>
       <c r="K376" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L376" t="s">
         <v>2758</v>
@@ -22945,7 +22945,7 @@
         <v>0</v>
       </c>
       <c r="K377" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L377" t="s">
         <v>2758</v>
@@ -22983,7 +22983,7 @@
         <v>0</v>
       </c>
       <c r="K378" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L378" t="s">
         <v>2758</v>
@@ -23021,7 +23021,7 @@
         <v>0</v>
       </c>
       <c r="K379" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L379" t="s">
         <v>2758</v>
@@ -23059,7 +23059,7 @@
         <v>0</v>
       </c>
       <c r="K380" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L380" t="s">
         <v>2758</v>
@@ -23097,7 +23097,7 @@
         <v>0</v>
       </c>
       <c r="K381" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L381" t="s">
         <v>2758</v>
@@ -23135,7 +23135,7 @@
         <v>0</v>
       </c>
       <c r="K382" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L382" t="s">
         <v>2758</v>
@@ -23173,7 +23173,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L383" t="s">
         <v>2758</v>
@@ -23211,7 +23211,7 @@
         <v>0</v>
       </c>
       <c r="K384" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L384" t="s">
         <v>2758</v>
@@ -23249,7 +23249,7 @@
         <v>0</v>
       </c>
       <c r="K385" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L385" t="s">
         <v>2758</v>
@@ -23287,7 +23287,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L386" t="s">
         <v>2758</v>
@@ -23325,7 +23325,7 @@
         <v>0</v>
       </c>
       <c r="K387" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L387" t="s">
         <v>2758</v>
@@ -23339,7 +23339,7 @@
         <v>773</v>
       </c>
       <c r="C388" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="D388">
         <v>36</v>
@@ -23363,7 +23363,7 @@
         <v>0</v>
       </c>
       <c r="K388" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L388" t="s">
         <v>2758</v>
@@ -23401,7 +23401,7 @@
         <v>0</v>
       </c>
       <c r="K389" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L389" t="s">
         <v>2758</v>
@@ -23439,7 +23439,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L390" t="s">
         <v>2758</v>
@@ -23477,7 +23477,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L391" t="s">
         <v>2758</v>
@@ -23515,7 +23515,7 @@
         <v>0</v>
       </c>
       <c r="K392" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L392" t="s">
         <v>2758</v>
@@ -23553,7 +23553,7 @@
         <v>0</v>
       </c>
       <c r="K393" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L393" t="s">
         <v>2758</v>
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L394" t="s">
         <v>2758</v>
@@ -23629,7 +23629,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L395" t="s">
         <v>2758</v>
@@ -23667,7 +23667,7 @@
         <v>0</v>
       </c>
       <c r="K396" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L396" t="s">
         <v>2758</v>
@@ -23705,7 +23705,7 @@
         <v>0</v>
       </c>
       <c r="K397" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L397" t="s">
         <v>2758</v>
@@ -23743,7 +23743,7 @@
         <v>0</v>
       </c>
       <c r="K398" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L398" t="s">
         <v>2758</v>
@@ -23781,7 +23781,7 @@
         <v>0</v>
       </c>
       <c r="K399" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L399" t="s">
         <v>2758</v>
@@ -23819,7 +23819,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L400" t="s">
         <v>2758</v>
@@ -23857,7 +23857,7 @@
         <v>0</v>
       </c>
       <c r="K401" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L401" t="s">
         <v>2758</v>
@@ -23895,7 +23895,7 @@
         <v>0</v>
       </c>
       <c r="K402" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L402" t="s">
         <v>2758</v>
@@ -23933,7 +23933,7 @@
         <v>0</v>
       </c>
       <c r="K403" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L403" t="s">
         <v>2758</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="K404" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L404" t="s">
         <v>2758</v>
@@ -24009,7 +24009,7 @@
         <v>0</v>
       </c>
       <c r="K405" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L405" t="s">
         <v>2758</v>
@@ -24047,7 +24047,7 @@
         <v>0</v>
       </c>
       <c r="K406" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L406" t="s">
         <v>2758</v>
@@ -24085,7 +24085,7 @@
         <v>0</v>
       </c>
       <c r="K407" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L407" t="s">
         <v>2758</v>
@@ -24123,7 +24123,7 @@
         <v>0</v>
       </c>
       <c r="K408" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L408" t="s">
         <v>2758</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="K409" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L409" t="s">
         <v>2758</v>
@@ -24199,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="K410" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L410" t="s">
         <v>2758</v>
@@ -24237,7 +24237,7 @@
         <v>0</v>
       </c>
       <c r="K411" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L411" t="s">
         <v>2758</v>
@@ -24275,7 +24275,7 @@
         <v>0</v>
       </c>
       <c r="K412" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L412" t="s">
         <v>2758</v>
@@ -24313,7 +24313,7 @@
         <v>0</v>
       </c>
       <c r="K413" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L413" t="s">
         <v>2758</v>
@@ -24351,7 +24351,7 @@
         <v>0</v>
       </c>
       <c r="K414" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L414" t="s">
         <v>2758</v>
@@ -24389,7 +24389,7 @@
         <v>0</v>
       </c>
       <c r="K415" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L415" t="s">
         <v>2758</v>
@@ -24427,7 +24427,7 @@
         <v>0</v>
       </c>
       <c r="K416" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L416" t="s">
         <v>2758</v>
@@ -24465,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="K417" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L417" t="s">
         <v>2758</v>
@@ -24503,7 +24503,7 @@
         <v>0</v>
       </c>
       <c r="K418" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L418" t="s">
         <v>2758</v>
@@ -24541,7 +24541,7 @@
         <v>0</v>
       </c>
       <c r="K419" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L419" t="s">
         <v>2758</v>
@@ -24579,7 +24579,7 @@
         <v>0</v>
       </c>
       <c r="K420" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L420" t="s">
         <v>2758</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="K421" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L421" t="s">
         <v>2758</v>
@@ -24655,7 +24655,7 @@
         <v>0</v>
       </c>
       <c r="K422" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L422" t="s">
         <v>2758</v>
@@ -24693,7 +24693,7 @@
         <v>0</v>
       </c>
       <c r="K423" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L423" t="s">
         <v>2758</v>
@@ -24731,7 +24731,7 @@
         <v>0</v>
       </c>
       <c r="K424" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L424" t="s">
         <v>2758</v>
@@ -24769,7 +24769,7 @@
         <v>0</v>
       </c>
       <c r="K425" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L425" t="s">
         <v>2758</v>
@@ -24807,7 +24807,7 @@
         <v>0</v>
       </c>
       <c r="K426" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L426" t="s">
         <v>2758</v>
@@ -24845,7 +24845,7 @@
         <v>0</v>
       </c>
       <c r="K427" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L427" t="s">
         <v>2758</v>
@@ -24883,7 +24883,7 @@
         <v>0</v>
       </c>
       <c r="K428" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L428" t="s">
         <v>2758</v>
@@ -24921,7 +24921,7 @@
         <v>0</v>
       </c>
       <c r="K429" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L429" t="s">
         <v>2758</v>
@@ -24959,7 +24959,7 @@
         <v>0</v>
       </c>
       <c r="K430" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L430" t="s">
         <v>2758</v>
@@ -24997,7 +24997,7 @@
         <v>0</v>
       </c>
       <c r="K431" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L431" t="s">
         <v>2758</v>
@@ -25035,7 +25035,7 @@
         <v>0</v>
       </c>
       <c r="K432" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L432" t="s">
         <v>2758</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="K433" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L433" t="s">
         <v>2758</v>
@@ -25111,7 +25111,7 @@
         <v>0</v>
       </c>
       <c r="K434" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L434" t="s">
         <v>2758</v>
@@ -25149,7 +25149,7 @@
         <v>0</v>
       </c>
       <c r="K435" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L435" t="s">
         <v>2758</v>
@@ -25187,7 +25187,7 @@
         <v>0</v>
       </c>
       <c r="K436" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L436" t="s">
         <v>2758</v>
@@ -25225,7 +25225,7 @@
         <v>0</v>
       </c>
       <c r="K437" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L437" t="s">
         <v>2758</v>
@@ -25263,7 +25263,7 @@
         <v>0</v>
       </c>
       <c r="K438" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L438" t="s">
         <v>2758</v>
@@ -25301,7 +25301,7 @@
         <v>0</v>
       </c>
       <c r="K439" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L439" t="s">
         <v>2758</v>
@@ -25339,7 +25339,7 @@
         <v>0</v>
       </c>
       <c r="K440" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L440" t="s">
         <v>2758</v>
@@ -25377,7 +25377,7 @@
         <v>0</v>
       </c>
       <c r="K441" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L441" t="s">
         <v>2758</v>
@@ -25415,7 +25415,7 @@
         <v>0</v>
       </c>
       <c r="K442" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L442" t="s">
         <v>2758</v>
@@ -25453,7 +25453,7 @@
         <v>0</v>
       </c>
       <c r="K443" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L443" t="s">
         <v>2758</v>
@@ -25491,7 +25491,7 @@
         <v>0</v>
       </c>
       <c r="K444" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L444" t="s">
         <v>2758</v>
@@ -25529,7 +25529,7 @@
         <v>0</v>
       </c>
       <c r="K445" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L445" t="s">
         <v>2758</v>
@@ -25567,7 +25567,7 @@
         <v>0</v>
       </c>
       <c r="K446" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L446" t="s">
         <v>2758</v>
@@ -25605,7 +25605,7 @@
         <v>0</v>
       </c>
       <c r="K447" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L447" t="s">
         <v>2758</v>
@@ -25643,7 +25643,7 @@
         <v>0</v>
       </c>
       <c r="K448" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L448" t="s">
         <v>2758</v>
@@ -25681,7 +25681,7 @@
         <v>0</v>
       </c>
       <c r="K449" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L449" t="s">
         <v>2758</v>
@@ -25719,7 +25719,7 @@
         <v>0</v>
       </c>
       <c r="K450" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L450" t="s">
         <v>2758</v>
@@ -25757,7 +25757,7 @@
         <v>0</v>
       </c>
       <c r="K451" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L451" t="s">
         <v>2758</v>
@@ -25795,7 +25795,7 @@
         <v>0</v>
       </c>
       <c r="K452" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L452" t="s">
         <v>2758</v>
@@ -25833,7 +25833,7 @@
         <v>0</v>
       </c>
       <c r="K453" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L453" t="s">
         <v>2758</v>
@@ -25871,7 +25871,7 @@
         <v>0</v>
       </c>
       <c r="K454" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L454" t="s">
         <v>2758</v>
@@ -25909,7 +25909,7 @@
         <v>0</v>
       </c>
       <c r="K455" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L455" t="s">
         <v>2758</v>
@@ -25947,7 +25947,7 @@
         <v>0</v>
       </c>
       <c r="K456" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L456" t="s">
         <v>2758</v>
@@ -25985,7 +25985,7 @@
         <v>0</v>
       </c>
       <c r="K457" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L457" t="s">
         <v>2758</v>
@@ -26023,7 +26023,7 @@
         <v>0</v>
       </c>
       <c r="K458" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L458" t="s">
         <v>2758</v>
@@ -26061,7 +26061,7 @@
         <v>0</v>
       </c>
       <c r="K459" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L459" t="s">
         <v>2758</v>
@@ -26099,7 +26099,7 @@
         <v>0</v>
       </c>
       <c r="K460" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L460" t="s">
         <v>2758</v>
@@ -26137,7 +26137,7 @@
         <v>0</v>
       </c>
       <c r="K461" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L461" t="s">
         <v>2758</v>
@@ -26175,7 +26175,7 @@
         <v>0</v>
       </c>
       <c r="K462" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L462" t="s">
         <v>2758</v>
@@ -26213,7 +26213,7 @@
         <v>0</v>
       </c>
       <c r="K463" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L463" t="s">
         <v>2758</v>
@@ -26251,7 +26251,7 @@
         <v>0</v>
       </c>
       <c r="K464" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L464" t="s">
         <v>2758</v>
@@ -26289,7 +26289,7 @@
         <v>0</v>
       </c>
       <c r="K465" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L465" t="s">
         <v>2758</v>
@@ -26327,7 +26327,7 @@
         <v>0</v>
       </c>
       <c r="K466" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L466" t="s">
         <v>2758</v>
@@ -26365,7 +26365,7 @@
         <v>0</v>
       </c>
       <c r="K467" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L467" t="s">
         <v>2758</v>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="K468" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L468" t="s">
         <v>2758</v>
@@ -26441,7 +26441,7 @@
         <v>0</v>
       </c>
       <c r="K469" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L469" t="s">
         <v>2758</v>
@@ -26479,7 +26479,7 @@
         <v>0</v>
       </c>
       <c r="K470" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L470" t="s">
         <v>2758</v>
@@ -26517,7 +26517,7 @@
         <v>0</v>
       </c>
       <c r="K471" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L471" t="s">
         <v>2758</v>
@@ -26555,7 +26555,7 @@
         <v>0</v>
       </c>
       <c r="K472" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L472" t="s">
         <v>2758</v>
@@ -26593,7 +26593,7 @@
         <v>0</v>
       </c>
       <c r="K473" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L473" t="s">
         <v>2758</v>
@@ -26631,7 +26631,7 @@
         <v>0</v>
       </c>
       <c r="K474" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L474" t="s">
         <v>2758</v>
@@ -26669,7 +26669,7 @@
         <v>0</v>
       </c>
       <c r="K475" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L475" t="s">
         <v>2758</v>
@@ -26707,7 +26707,7 @@
         <v>0</v>
       </c>
       <c r="K476" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L476" t="s">
         <v>2758</v>
@@ -26745,7 +26745,7 @@
         <v>0</v>
       </c>
       <c r="K477" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L477" t="s">
         <v>2758</v>
@@ -26783,7 +26783,7 @@
         <v>0</v>
       </c>
       <c r="K478" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L478" t="s">
         <v>2758</v>
@@ -26821,7 +26821,7 @@
         <v>0</v>
       </c>
       <c r="K479" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L479" t="s">
         <v>2758</v>
@@ -26859,7 +26859,7 @@
         <v>0</v>
       </c>
       <c r="K480" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L480" t="s">
         <v>2758</v>
@@ -26897,7 +26897,7 @@
         <v>0</v>
       </c>
       <c r="K481" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L481" t="s">
         <v>2758</v>
@@ -26935,7 +26935,7 @@
         <v>0</v>
       </c>
       <c r="K482" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L482" t="s">
         <v>2758</v>
@@ -26973,7 +26973,7 @@
         <v>0</v>
       </c>
       <c r="K483" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L483" t="s">
         <v>2758</v>
@@ -27011,7 +27011,7 @@
         <v>0</v>
       </c>
       <c r="K484" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L484" t="s">
         <v>2758</v>
@@ -27049,7 +27049,7 @@
         <v>0</v>
       </c>
       <c r="K485" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L485" t="s">
         <v>2758</v>
@@ -27087,7 +27087,7 @@
         <v>0</v>
       </c>
       <c r="K486" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L486" t="s">
         <v>2758</v>
@@ -27125,7 +27125,7 @@
         <v>0</v>
       </c>
       <c r="K487" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L487" t="s">
         <v>2758</v>
@@ -27163,7 +27163,7 @@
         <v>0</v>
       </c>
       <c r="K488" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L488" t="s">
         <v>2758</v>
@@ -27201,7 +27201,7 @@
         <v>0</v>
       </c>
       <c r="K489" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L489" t="s">
         <v>2758</v>
@@ -27239,7 +27239,7 @@
         <v>0</v>
       </c>
       <c r="K490" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L490" t="s">
         <v>2758</v>
@@ -27250,23 +27250,26 @@
         <v>413</v>
       </c>
       <c r="B491" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C491" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="D491">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E491" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="F491" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="G491" t="s">
         <v>2468</v>
       </c>
+      <c r="H491" t="s">
+        <v>2748</v>
+      </c>
       <c r="I491">
         <v>1</v>
       </c>
@@ -27274,10 +27277,10 @@
         <v>0</v>
       </c>
       <c r="K491" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="L491" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="492" spans="1:12">
@@ -27285,26 +27288,23 @@
         <v>414</v>
       </c>
       <c r="B492" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C492" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D492">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E492" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="F492" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="G492" t="s">
         <v>2469</v>
       </c>
-      <c r="H492" t="s">
-        <v>2748</v>
-      </c>
       <c r="I492">
         <v>1</v>
       </c>
@@ -27312,10 +27312,10 @@
         <v>0</v>
       </c>
       <c r="K492" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="L492" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="493" spans="1:12">
@@ -27350,7 +27350,7 @@
         <v>0</v>
       </c>
       <c r="K493" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L493" t="s">
         <v>2758</v>
@@ -27388,7 +27388,7 @@
         <v>0</v>
       </c>
       <c r="K494" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L494" t="s">
         <v>2758</v>
@@ -27426,7 +27426,7 @@
         <v>0</v>
       </c>
       <c r="K495" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L495" t="s">
         <v>2758</v>
@@ -27464,7 +27464,7 @@
         <v>0</v>
       </c>
       <c r="K496" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L496" t="s">
         <v>2758</v>
@@ -27502,7 +27502,7 @@
         <v>0</v>
       </c>
       <c r="K497" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L497" t="s">
         <v>2758</v>
@@ -27540,7 +27540,7 @@
         <v>0</v>
       </c>
       <c r="K498" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L498" t="s">
         <v>2758</v>
@@ -27578,7 +27578,7 @@
         <v>0</v>
       </c>
       <c r="K499" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L499" t="s">
         <v>2758</v>
@@ -27616,7 +27616,7 @@
         <v>0</v>
       </c>
       <c r="K500" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L500" t="s">
         <v>2758</v>
@@ -27654,7 +27654,7 @@
         <v>0</v>
       </c>
       <c r="K501" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L501" t="s">
         <v>2758</v>
